--- a/LogoJ_Platform_Rest_Test/bin/Debug/Template/Muhasebe Gunluk Fisi.xlsx
+++ b/LogoJ_Platform_Rest_Test/bin/Debug/Template/Muhasebe Gunluk Fisi.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DOGUKAN\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DOGUKAN\source\repos\LogoJ_Platform_Rest_Test\LogoJ_Platform_Rest_Test\bin\Debug\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FA4F10-538D-4AE6-9BAA-6115C9C298DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA638B6-29C5-4331-AD4A-7900F03078BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9711E6CE-5FD9-4707-B709-915BBF0C49A5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9711E6CE-5FD9-4707-B709-915BBF0C49A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Muhasebe Fişi" sheetId="3" r:id="rId1"/>
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="51">
   <si>
     <t>TARIH</t>
   </si>
@@ -228,15 +228,6 @@
     <t>HZ</t>
   </si>
   <si>
-    <t>A40801130</t>
-  </si>
-  <si>
-    <t>X40801131</t>
-  </si>
-  <si>
-    <t>A40801135</t>
-  </si>
-  <si>
     <t>740.001.004</t>
   </si>
   <si>
@@ -255,25 +246,34 @@
     <t>740.001.001</t>
   </si>
   <si>
-    <t>2024 7 Bordro Fisi - Actual Payroll Fazla Mesai</t>
+    <t>01</t>
   </si>
   <si>
-    <t>2024 7 Bordro Fisi - Actual Payroll Ayni Yardim</t>
+    <t>25081018303851100062</t>
   </si>
   <si>
-    <t>2024 7 Bordro Fisi - Actual Payroll Yemek Yardimi SGK Dahil</t>
+    <t>25081018303851100063</t>
   </si>
   <si>
-    <t>2024 7 Bordro Fisi - Actual Payroll SGK Isveren (Indirimli)</t>
+    <t>25081018303851100064</t>
   </si>
   <si>
-    <t>2024 7 Bordro Fisi - Actual Payroll SGK Isveren Issizlik Payi</t>
+    <t>2025 7 Bordro Fisi - Actual Payroll Ayni Yardim</t>
   </si>
   <si>
-    <t>2024 7 Bordro Fisi - Actual Payroll Normal calisma Gunu</t>
+    <t>2025 7 Bordro Fisi - Actual Payroll Yemek Yardimi SGK Dahil</t>
   </si>
   <si>
-    <t>Actual Payroll 2024-07</t>
+    <t>2025 7 Bordro Fisi - Actual Payroll SGK Isveren (Indirimli)</t>
+  </si>
+  <si>
+    <t>2025 7 Bordro Fisi - Actual Payroll SGK Isveren Issizlik Payi</t>
+  </si>
+  <si>
+    <t>2025 7 Bordro Fisi - Actual Payroll Normal calisma Gunu</t>
+  </si>
+  <si>
+    <t>Actual Payroll 2025-07</t>
   </si>
 </sst>
 </file>
@@ -283,7 +283,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -418,14 +418,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="162"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -458,14 +465,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -510,19 +511,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -586,14 +574,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="17" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1"/>
   </cellXfs>
   <cellStyles count="17">
     <cellStyle name="Giriş 2" xfId="13" xr:uid="{26C81C11-CC4B-4025-B09D-5E7408D276C6}"/>
@@ -928,27 +916,27 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Q472"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.88671875" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" customWidth="1"/>
-    <col min="7" max="7" width="26.5546875" customWidth="1"/>
-    <col min="8" max="8" width="26.33203125" customWidth="1"/>
-    <col min="9" max="9" width="19.44140625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" customWidth="1"/>
+    <col min="7" max="7" width="26.5703125" customWidth="1"/>
+    <col min="8" max="8" width="26.28515625" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" style="3" customWidth="1"/>
     <col min="10" max="10" width="18" style="3" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="61.109375" customWidth="1"/>
-    <col min="14" max="14" width="28.88671875" customWidth="1"/>
-    <col min="15" max="15" width="64.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="61.140625" customWidth="1"/>
+    <col min="14" max="14" width="28.85546875" customWidth="1"/>
+    <col min="15" max="15" width="64.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>12</v>
       </c>
@@ -998,31 +986,33 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="25">
+      <c r="B2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="23">
         <v>45874</v>
       </c>
-      <c r="D2" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>35</v>
+      <c r="D2" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>42</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" t="s">
         <v>29</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2" s="17">
+        <v>35</v>
+      </c>
+      <c r="I2" s="29">
         <v>130266.45</v>
       </c>
-      <c r="J2" s="23"/>
+      <c r="J2" s="22"/>
       <c r="K2" t="s">
         <v>13</v>
       </c>
@@ -1030,7 +1020,7 @@
         <v>1</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="O2" s="9" t="s">
         <v>50</v>
@@ -1039,28 +1029,30 @@
         <v>17251028</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="25">
+      <c r="B3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="23">
         <v>45874</v>
       </c>
-      <c r="D3" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>35</v>
+      <c r="D3" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>42</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" t="s">
         <v>31</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="17">
+        <v>36</v>
+      </c>
+      <c r="I3" s="29">
         <v>51740.92</v>
       </c>
       <c r="J3" s="4"/>
@@ -1080,28 +1072,30 @@
         <v>17251033</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="25">
+      <c r="B4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="23">
         <v>45874</v>
       </c>
-      <c r="D4" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>35</v>
+      <c r="D4" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>42</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="17">
+      <c r="H4" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="29">
         <v>5268.87</v>
       </c>
       <c r="J4" s="4"/>
@@ -1121,28 +1115,30 @@
         <v>17251034</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="25">
+      <c r="B5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="23">
         <v>45874</v>
       </c>
-      <c r="D5" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>35</v>
+      <c r="D5" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>42</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="I5" s="17"/>
+      <c r="H5" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="29"/>
       <c r="J5" s="5">
         <v>187276.24</v>
       </c>
@@ -1162,28 +1158,30 @@
         <v>17251035</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="25">
+      <c r="B6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="23">
         <v>45875</v>
       </c>
-      <c r="D6" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>36</v>
+      <c r="D6" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>43</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" t="s">
         <v>29</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="17">
+        <v>39</v>
+      </c>
+      <c r="I6" s="29">
         <v>89688.99</v>
       </c>
       <c r="J6" s="4"/>
@@ -1203,28 +1201,30 @@
         <v>17251040</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="25">
+      <c r="B7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="23">
         <v>45875</v>
       </c>
-      <c r="D7" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>36</v>
+      <c r="D7" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>43</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" t="s">
         <v>29</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="I7" s="17"/>
+        <v>40</v>
+      </c>
+      <c r="I7" s="29"/>
       <c r="J7" s="5">
         <v>89688.99</v>
       </c>
@@ -1244,28 +1244,30 @@
         <v>17251042</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="25">
+      <c r="B8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="23">
         <v>45874</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>37</v>
+      <c r="D8" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>44</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" t="s">
         <v>29</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" s="17">
+        <v>35</v>
+      </c>
+      <c r="I8" s="29">
         <v>130266.45</v>
       </c>
       <c r="J8" s="4"/>
@@ -1273,10 +1275,10 @@
         <v>32</v>
       </c>
       <c r="L8">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="O8" s="9" t="s">
         <v>50</v>
@@ -1285,28 +1287,30 @@
         <v>17251028</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="25">
+      <c r="B9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="23">
         <v>45874</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>37</v>
+      <c r="D9" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>44</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" t="s">
         <v>31</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9" s="17">
+        <v>36</v>
+      </c>
+      <c r="I9" s="29">
         <v>51740.92</v>
       </c>
       <c r="J9" s="4"/>
@@ -1314,7 +1318,7 @@
         <v>33</v>
       </c>
       <c r="L9">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="M9" s="9" t="s">
         <v>45</v>
@@ -1326,28 +1330,30 @@
         <v>17251033</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="25">
+      <c r="B10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="23">
         <v>45874</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>37</v>
+      <c r="D10" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>44</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" s="17">
+      <c r="H10" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="29">
         <v>5268.87</v>
       </c>
       <c r="J10" s="4"/>
@@ -1367,26 +1373,28 @@
         <v>17251034</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="25">
+      <c r="B11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="23">
         <v>45874</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>37</v>
+      <c r="D11" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>44</v>
       </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="24" t="s">
+      <c r="G11" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="29" t="s">
-        <v>41</v>
+      <c r="H11" s="25" t="s">
+        <v>38</v>
       </c>
       <c r="I11" s="17"/>
       <c r="J11" s="5">
@@ -1408,7 +1416,7 @@
         <v>17251035</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="19"/>
@@ -1420,7 +1428,7 @@
       <c r="O12" s="19"/>
       <c r="P12" s="20"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="19"/>
@@ -1432,7 +1440,7 @@
       <c r="O13" s="19"/>
       <c r="P13" s="20"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="19"/>
@@ -1444,7 +1452,7 @@
       <c r="O14" s="19"/>
       <c r="P14" s="20"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="19"/>
@@ -1456,7 +1464,7 @@
       <c r="O15" s="19"/>
       <c r="P15" s="20"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="19"/>
@@ -1468,7 +1476,7 @@
       <c r="O16" s="19"/>
       <c r="P16" s="20"/>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="19"/>
@@ -1480,7 +1488,7 @@
       <c r="O17" s="19"/>
       <c r="P17" s="20"/>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="19"/>
@@ -1491,7 +1499,7 @@
       <c r="O18" s="19"/>
       <c r="P18" s="20"/>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="19"/>
@@ -1502,7 +1510,7 @@
       <c r="O19" s="19"/>
       <c r="P19" s="20"/>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="19"/>
@@ -1513,7 +1521,7 @@
       <c r="O20" s="19"/>
       <c r="P20" s="20"/>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="19"/>
@@ -1524,7 +1532,7 @@
       <c r="O21" s="19"/>
       <c r="P21" s="20"/>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="19"/>
@@ -1535,7 +1543,7 @@
       <c r="O22" s="19"/>
       <c r="P22" s="20"/>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="19"/>
@@ -1546,7 +1554,7 @@
       <c r="O23" s="19"/>
       <c r="P23" s="20"/>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="19"/>
@@ -1557,7 +1565,7 @@
       <c r="O24" s="19"/>
       <c r="P24" s="20"/>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="19"/>
@@ -1568,7 +1576,7 @@
       <c r="O25" s="19"/>
       <c r="P25" s="20"/>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="19"/>
@@ -1579,7 +1587,7 @@
       <c r="O26" s="19"/>
       <c r="P26" s="20"/>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="19"/>
@@ -1590,7 +1598,7 @@
       <c r="O27" s="19"/>
       <c r="P27" s="20"/>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="19"/>
@@ -1601,7 +1609,7 @@
       <c r="O28" s="19"/>
       <c r="P28" s="20"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="19"/>
@@ -1612,7 +1620,7 @@
       <c r="O29" s="19"/>
       <c r="P29" s="20"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="19"/>
@@ -1623,7 +1631,7 @@
       <c r="O30" s="19"/>
       <c r="P30" s="20"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="19"/>
@@ -1634,7 +1642,7 @@
       <c r="O31" s="19"/>
       <c r="P31" s="20"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="19"/>
@@ -1645,7 +1653,7 @@
       <c r="O32" s="19"/>
       <c r="P32" s="20"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="19"/>
@@ -1657,18 +1665,18 @@
       <c r="P33" s="20"/>
       <c r="Q33" s="9"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="19"/>
-      <c r="H34" s="22"/>
+      <c r="H34" s="26"/>
       <c r="I34" s="5"/>
       <c r="J34" s="18"/>
       <c r="M34" s="19"/>
       <c r="O34" s="19"/>
       <c r="P34" s="4"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D35" s="2"/>
       <c r="E35" s="10"/>
       <c r="H35" s="4"/>
@@ -1678,7 +1686,7 @@
       <c r="O35" s="10"/>
       <c r="P35" s="4"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D36" s="2"/>
       <c r="E36" s="10"/>
       <c r="H36" s="4"/>
@@ -1688,7 +1696,7 @@
       <c r="O36" s="10"/>
       <c r="P36" s="4"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D37" s="2"/>
       <c r="E37" s="10"/>
       <c r="H37" s="4"/>
@@ -1698,7 +1706,7 @@
       <c r="O37" s="10"/>
       <c r="P37" s="4"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D38" s="2"/>
       <c r="E38" s="10"/>
       <c r="H38" s="4"/>
@@ -1708,7 +1716,7 @@
       <c r="O38" s="10"/>
       <c r="P38" s="4"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D39" s="2"/>
       <c r="E39" s="10"/>
       <c r="H39" s="4"/>
@@ -1718,7 +1726,7 @@
       <c r="O39" s="10"/>
       <c r="P39" s="4"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D40" s="2"/>
       <c r="E40" s="10"/>
       <c r="H40" s="4"/>
@@ -1728,7 +1736,7 @@
       <c r="O40" s="10"/>
       <c r="P40" s="4"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D41" s="2"/>
       <c r="E41" s="10"/>
       <c r="H41" s="4"/>
@@ -1738,7 +1746,7 @@
       <c r="O41" s="10"/>
       <c r="P41" s="4"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D42" s="2"/>
       <c r="E42" s="10"/>
       <c r="H42" s="4"/>
@@ -1748,7 +1756,7 @@
       <c r="O42" s="10"/>
       <c r="P42" s="4"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D43" s="2"/>
       <c r="E43" s="10"/>
       <c r="H43" s="4"/>
@@ -1758,7 +1766,7 @@
       <c r="O43" s="10"/>
       <c r="P43" s="4"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D44" s="2"/>
       <c r="E44" s="10"/>
       <c r="H44" s="4"/>
@@ -1768,7 +1776,7 @@
       <c r="O44" s="10"/>
       <c r="P44" s="4"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D45" s="2"/>
       <c r="E45" s="10"/>
       <c r="H45" s="4"/>
@@ -1778,7 +1786,7 @@
       <c r="O45" s="10"/>
       <c r="P45" s="4"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D46" s="2"/>
       <c r="E46" s="10"/>
       <c r="H46" s="4"/>
@@ -1788,7 +1796,7 @@
       <c r="O46" s="10"/>
       <c r="P46" s="4"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D47" s="2"/>
       <c r="E47" s="10"/>
       <c r="H47" s="4"/>
@@ -1798,7 +1806,7 @@
       <c r="O47" s="10"/>
       <c r="P47" s="4"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D48" s="2"/>
       <c r="E48" s="10"/>
       <c r="H48" s="4"/>
@@ -1808,7 +1816,7 @@
       <c r="O48" s="10"/>
       <c r="P48" s="4"/>
     </row>
-    <row r="49" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D49" s="2"/>
       <c r="E49" s="10"/>
       <c r="H49" s="4"/>
@@ -1818,7 +1826,7 @@
       <c r="O49" s="10"/>
       <c r="P49" s="4"/>
     </row>
-    <row r="50" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D50" s="2"/>
       <c r="E50" s="10"/>
       <c r="H50" s="4"/>
@@ -1828,7 +1836,7 @@
       <c r="O50" s="10"/>
       <c r="P50" s="4"/>
     </row>
-    <row r="51" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D51" s="2"/>
       <c r="E51" s="10"/>
       <c r="H51" s="4"/>
@@ -1838,7 +1846,7 @@
       <c r="O51" s="10"/>
       <c r="P51" s="4"/>
     </row>
-    <row r="52" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D52" s="2"/>
       <c r="E52" s="10"/>
       <c r="H52" s="4"/>
@@ -1848,7 +1856,7 @@
       <c r="O52" s="10"/>
       <c r="P52" s="4"/>
     </row>
-    <row r="53" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D53" s="2"/>
       <c r="E53" s="10"/>
       <c r="H53" s="4"/>
@@ -1858,7 +1866,7 @@
       <c r="O53" s="10"/>
       <c r="P53" s="4"/>
     </row>
-    <row r="54" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D54" s="2"/>
       <c r="E54" s="10"/>
       <c r="H54" s="4"/>
@@ -1868,7 +1876,7 @@
       <c r="O54" s="10"/>
       <c r="P54" s="4"/>
     </row>
-    <row r="55" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D55" s="2"/>
       <c r="E55" s="10"/>
       <c r="H55" s="4"/>
@@ -1878,7 +1886,7 @@
       <c r="O55" s="10"/>
       <c r="P55" s="4"/>
     </row>
-    <row r="56" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D56" s="2"/>
       <c r="E56" s="10"/>
       <c r="H56" s="4"/>
@@ -1888,7 +1896,7 @@
       <c r="O56" s="10"/>
       <c r="P56" s="4"/>
     </row>
-    <row r="57" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D57" s="2"/>
       <c r="E57" s="10"/>
       <c r="H57" s="4"/>
@@ -1898,7 +1906,7 @@
       <c r="O57" s="10"/>
       <c r="P57" s="4"/>
     </row>
-    <row r="58" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D58" s="2"/>
       <c r="E58" s="10"/>
       <c r="H58" s="4"/>
@@ -1908,7 +1916,7 @@
       <c r="O58" s="10"/>
       <c r="P58" s="4"/>
     </row>
-    <row r="59" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D59" s="2"/>
       <c r="E59" s="10"/>
       <c r="H59" s="4"/>
@@ -1918,7 +1926,7 @@
       <c r="O59" s="10"/>
       <c r="P59" s="4"/>
     </row>
-    <row r="60" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D60" s="2"/>
       <c r="E60" s="10"/>
       <c r="H60" s="4"/>
@@ -1928,7 +1936,7 @@
       <c r="O60" s="10"/>
       <c r="P60" s="4"/>
     </row>
-    <row r="61" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D61" s="2"/>
       <c r="E61" s="10"/>
       <c r="H61" s="4"/>
@@ -1938,7 +1946,7 @@
       <c r="O61" s="10"/>
       <c r="P61" s="4"/>
     </row>
-    <row r="62" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D62" s="2"/>
       <c r="E62" s="10"/>
       <c r="H62" s="4"/>
@@ -1948,7 +1956,7 @@
       <c r="O62" s="10"/>
       <c r="P62" s="4"/>
     </row>
-    <row r="63" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D63" s="2"/>
       <c r="E63" s="10"/>
       <c r="H63" s="4"/>
@@ -1958,7 +1966,7 @@
       <c r="O63" s="10"/>
       <c r="P63" s="4"/>
     </row>
-    <row r="64" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D64" s="2"/>
       <c r="E64" s="10"/>
       <c r="H64" s="4"/>
@@ -1968,7 +1976,7 @@
       <c r="O64" s="10"/>
       <c r="P64" s="4"/>
     </row>
-    <row r="65" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D65" s="2"/>
       <c r="E65" s="10"/>
       <c r="H65" s="4"/>
@@ -1978,7 +1986,7 @@
       <c r="O65" s="10"/>
       <c r="P65" s="4"/>
     </row>
-    <row r="66" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D66" s="2"/>
       <c r="E66" s="10"/>
       <c r="H66" s="4"/>
@@ -1988,7 +1996,7 @@
       <c r="O66" s="10"/>
       <c r="P66" s="4"/>
     </row>
-    <row r="67" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D67" s="2"/>
       <c r="E67" s="10"/>
       <c r="H67" s="4"/>
@@ -1998,7 +2006,7 @@
       <c r="O67" s="10"/>
       <c r="P67" s="4"/>
     </row>
-    <row r="68" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D68" s="2"/>
       <c r="E68" s="10"/>
       <c r="H68" s="4"/>
@@ -2008,7 +2016,7 @@
       <c r="O68" s="10"/>
       <c r="P68" s="4"/>
     </row>
-    <row r="69" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D69" s="2"/>
       <c r="E69" s="10"/>
       <c r="H69" s="4"/>
@@ -2018,7 +2026,7 @@
       <c r="O69" s="10"/>
       <c r="P69" s="4"/>
     </row>
-    <row r="70" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D70" s="2"/>
       <c r="E70" s="10"/>
       <c r="H70" s="4"/>
@@ -2028,7 +2036,7 @@
       <c r="O70" s="10"/>
       <c r="P70" s="4"/>
     </row>
-    <row r="71" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D71" s="2"/>
       <c r="E71" s="10"/>
       <c r="H71" s="4"/>
@@ -2038,7 +2046,7 @@
       <c r="O71" s="10"/>
       <c r="P71" s="4"/>
     </row>
-    <row r="72" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D72" s="2"/>
       <c r="E72" s="10"/>
       <c r="H72" s="4"/>
@@ -2048,7 +2056,7 @@
       <c r="O72" s="10"/>
       <c r="P72" s="4"/>
     </row>
-    <row r="73" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D73" s="2"/>
       <c r="E73" s="10"/>
       <c r="H73" s="4"/>
@@ -2058,7 +2066,7 @@
       <c r="O73" s="10"/>
       <c r="P73" s="4"/>
     </row>
-    <row r="74" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D74" s="2"/>
       <c r="E74" s="10"/>
       <c r="H74" s="4"/>
@@ -2068,7 +2076,7 @@
       <c r="O74" s="10"/>
       <c r="P74" s="4"/>
     </row>
-    <row r="75" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D75" s="2"/>
       <c r="E75" s="10"/>
       <c r="H75" s="4"/>
@@ -2078,7 +2086,7 @@
       <c r="O75" s="10"/>
       <c r="P75" s="4"/>
     </row>
-    <row r="76" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D76" s="2"/>
       <c r="E76" s="10"/>
       <c r="H76" s="4"/>
@@ -2088,7 +2096,7 @@
       <c r="O76" s="10"/>
       <c r="P76" s="4"/>
     </row>
-    <row r="77" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D77" s="2"/>
       <c r="E77" s="10"/>
       <c r="H77" s="4"/>
@@ -2098,7 +2106,7 @@
       <c r="O77" s="10"/>
       <c r="P77" s="4"/>
     </row>
-    <row r="78" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="78" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D78" s="2"/>
       <c r="E78" s="10"/>
       <c r="H78" s="4"/>
@@ -2108,7 +2116,7 @@
       <c r="O78" s="10"/>
       <c r="P78" s="4"/>
     </row>
-    <row r="79" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D79" s="2"/>
       <c r="E79" s="10"/>
       <c r="H79" s="4"/>
@@ -2118,7 +2126,7 @@
       <c r="O79" s="10"/>
       <c r="P79" s="4"/>
     </row>
-    <row r="80" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D80" s="2"/>
       <c r="E80" s="10"/>
       <c r="H80" s="4"/>
@@ -2128,7 +2136,7 @@
       <c r="O80" s="10"/>
       <c r="P80" s="4"/>
     </row>
-    <row r="81" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D81" s="2"/>
       <c r="E81" s="10"/>
       <c r="H81" s="4"/>
@@ -2138,7 +2146,7 @@
       <c r="O81" s="10"/>
       <c r="P81" s="4"/>
     </row>
-    <row r="82" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D82" s="2"/>
       <c r="E82" s="10"/>
       <c r="H82" s="4"/>
@@ -2148,7 +2156,7 @@
       <c r="O82" s="10"/>
       <c r="P82" s="4"/>
     </row>
-    <row r="83" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D83" s="2"/>
       <c r="E83" s="10"/>
       <c r="H83" s="4"/>
@@ -2158,7 +2166,7 @@
       <c r="O83" s="10"/>
       <c r="P83" s="4"/>
     </row>
-    <row r="84" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D84" s="2"/>
       <c r="E84" s="10"/>
       <c r="H84" s="4"/>
@@ -2168,7 +2176,7 @@
       <c r="O84" s="10"/>
       <c r="P84" s="4"/>
     </row>
-    <row r="85" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="85" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D85" s="2"/>
       <c r="E85" s="10"/>
       <c r="H85" s="4"/>
@@ -2178,7 +2186,7 @@
       <c r="O85" s="10"/>
       <c r="P85" s="4"/>
     </row>
-    <row r="86" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D86" s="2"/>
       <c r="E86" s="10"/>
       <c r="H86" s="4"/>
@@ -2188,7 +2196,7 @@
       <c r="O86" s="10"/>
       <c r="P86" s="4"/>
     </row>
-    <row r="87" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D87" s="2"/>
       <c r="E87" s="10"/>
       <c r="H87" s="4"/>
@@ -2198,7 +2206,7 @@
       <c r="O87" s="10"/>
       <c r="P87" s="4"/>
     </row>
-    <row r="88" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="88" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D88" s="2"/>
       <c r="E88" s="10"/>
       <c r="H88" s="4"/>
@@ -2208,7 +2216,7 @@
       <c r="O88" s="10"/>
       <c r="P88" s="4"/>
     </row>
-    <row r="89" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D89" s="2"/>
       <c r="E89" s="10"/>
       <c r="H89" s="4"/>
@@ -2218,7 +2226,7 @@
       <c r="O89" s="10"/>
       <c r="P89" s="4"/>
     </row>
-    <row r="90" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D90" s="2"/>
       <c r="E90" s="10"/>
       <c r="H90" s="4"/>
@@ -2228,7 +2236,7 @@
       <c r="O90" s="10"/>
       <c r="P90" s="4"/>
     </row>
-    <row r="91" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="91" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D91" s="2"/>
       <c r="E91" s="10"/>
       <c r="H91" s="4"/>
@@ -2238,7 +2246,7 @@
       <c r="O91" s="10"/>
       <c r="P91" s="4"/>
     </row>
-    <row r="92" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="92" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D92" s="2"/>
       <c r="E92" s="10"/>
       <c r="H92" s="4"/>
@@ -2248,7 +2256,7 @@
       <c r="O92" s="10"/>
       <c r="P92" s="4"/>
     </row>
-    <row r="93" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="93" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D93" s="2"/>
       <c r="E93" s="10"/>
       <c r="H93" s="4"/>
@@ -2258,7 +2266,7 @@
       <c r="O93" s="10"/>
       <c r="P93" s="4"/>
     </row>
-    <row r="94" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D94" s="2"/>
       <c r="E94" s="10"/>
       <c r="H94" s="4"/>
@@ -2268,7 +2276,7 @@
       <c r="O94" s="10"/>
       <c r="P94" s="4"/>
     </row>
-    <row r="95" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="95" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D95" s="2"/>
       <c r="E95" s="10"/>
       <c r="H95" s="4"/>
@@ -2278,7 +2286,7 @@
       <c r="O95" s="10"/>
       <c r="P95" s="4"/>
     </row>
-    <row r="96" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D96" s="2"/>
       <c r="E96" s="10"/>
       <c r="H96" s="4"/>
@@ -2288,7 +2296,7 @@
       <c r="O96" s="10"/>
       <c r="P96" s="4"/>
     </row>
-    <row r="97" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D97" s="2"/>
       <c r="E97" s="10"/>
       <c r="H97" s="4"/>
@@ -2298,7 +2306,7 @@
       <c r="O97" s="10"/>
       <c r="P97" s="4"/>
     </row>
-    <row r="98" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D98" s="2"/>
       <c r="E98" s="10"/>
       <c r="H98" s="4"/>
@@ -2308,7 +2316,7 @@
       <c r="O98" s="10"/>
       <c r="P98" s="4"/>
     </row>
-    <row r="99" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D99" s="2"/>
       <c r="E99" s="10"/>
       <c r="H99" s="4"/>
@@ -2318,7 +2326,7 @@
       <c r="O99" s="10"/>
       <c r="P99" s="4"/>
     </row>
-    <row r="100" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D100" s="2"/>
       <c r="E100" s="10"/>
       <c r="H100" s="4"/>
@@ -2328,7 +2336,7 @@
       <c r="O100" s="10"/>
       <c r="P100" s="4"/>
     </row>
-    <row r="101" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D101" s="2"/>
       <c r="E101" s="10"/>
       <c r="H101" s="4"/>
@@ -2338,7 +2346,7 @@
       <c r="O101" s="10"/>
       <c r="P101" s="4"/>
     </row>
-    <row r="102" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D102" s="2"/>
       <c r="E102" s="10"/>
       <c r="H102" s="4"/>
@@ -2348,7 +2356,7 @@
       <c r="O102" s="10"/>
       <c r="P102" s="4"/>
     </row>
-    <row r="103" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="103" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D103" s="2"/>
       <c r="E103" s="10"/>
       <c r="H103" s="4"/>
@@ -2358,7 +2366,7 @@
       <c r="O103" s="10"/>
       <c r="P103" s="4"/>
     </row>
-    <row r="104" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="104" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D104" s="2"/>
       <c r="E104" s="10"/>
       <c r="H104" s="4"/>
@@ -2368,7 +2376,7 @@
       <c r="O104" s="10"/>
       <c r="P104" s="4"/>
     </row>
-    <row r="105" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D105" s="2"/>
       <c r="E105" s="10"/>
       <c r="H105" s="4"/>
@@ -2378,7 +2386,7 @@
       <c r="O105" s="10"/>
       <c r="P105" s="4"/>
     </row>
-    <row r="106" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="106" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D106" s="2"/>
       <c r="E106" s="10"/>
       <c r="H106" s="4"/>
@@ -2388,7 +2396,7 @@
       <c r="O106" s="10"/>
       <c r="P106" s="4"/>
     </row>
-    <row r="107" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="107" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D107" s="2"/>
       <c r="E107" s="10"/>
       <c r="H107" s="4"/>
@@ -2398,7 +2406,7 @@
       <c r="O107" s="10"/>
       <c r="P107" s="4"/>
     </row>
-    <row r="108" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D108" s="2"/>
       <c r="E108" s="10"/>
       <c r="H108" s="4"/>
@@ -2408,7 +2416,7 @@
       <c r="O108" s="10"/>
       <c r="P108" s="4"/>
     </row>
-    <row r="109" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="109" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D109" s="2"/>
       <c r="E109" s="10"/>
       <c r="H109" s="4"/>
@@ -2418,7 +2426,7 @@
       <c r="O109" s="10"/>
       <c r="P109" s="4"/>
     </row>
-    <row r="110" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="110" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D110" s="2"/>
       <c r="E110" s="10"/>
       <c r="H110" s="4"/>
@@ -2428,7 +2436,7 @@
       <c r="O110" s="10"/>
       <c r="P110" s="4"/>
     </row>
-    <row r="111" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="111" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D111" s="2"/>
       <c r="E111" s="10"/>
       <c r="H111" s="4"/>
@@ -2438,7 +2446,7 @@
       <c r="O111" s="10"/>
       <c r="P111" s="4"/>
     </row>
-    <row r="112" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="112" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D112" s="2"/>
       <c r="E112" s="10"/>
       <c r="H112" s="4"/>
@@ -2448,7 +2456,7 @@
       <c r="O112" s="10"/>
       <c r="P112" s="4"/>
     </row>
-    <row r="113" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="113" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D113" s="2"/>
       <c r="E113" s="10"/>
       <c r="H113" s="4"/>
@@ -2458,7 +2466,7 @@
       <c r="O113" s="10"/>
       <c r="P113" s="4"/>
     </row>
-    <row r="114" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="114" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D114" s="2"/>
       <c r="E114" s="10"/>
       <c r="H114" s="4"/>
@@ -2468,7 +2476,7 @@
       <c r="O114" s="10"/>
       <c r="P114" s="4"/>
     </row>
-    <row r="115" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="115" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D115" s="2"/>
       <c r="E115" s="10"/>
       <c r="H115" s="4"/>
@@ -2478,7 +2486,7 @@
       <c r="O115" s="10"/>
       <c r="P115" s="4"/>
     </row>
-    <row r="116" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="116" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D116" s="2"/>
       <c r="E116" s="10"/>
       <c r="H116" s="4"/>
@@ -2488,7 +2496,7 @@
       <c r="O116" s="10"/>
       <c r="P116" s="4"/>
     </row>
-    <row r="117" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="117" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D117" s="2"/>
       <c r="E117" s="10"/>
       <c r="H117" s="4"/>
@@ -2498,7 +2506,7 @@
       <c r="O117" s="10"/>
       <c r="P117" s="4"/>
     </row>
-    <row r="118" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="118" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D118" s="2"/>
       <c r="E118" s="10"/>
       <c r="H118" s="4"/>
@@ -2508,7 +2516,7 @@
       <c r="O118" s="10"/>
       <c r="P118" s="4"/>
     </row>
-    <row r="119" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="119" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D119" s="2"/>
       <c r="E119" s="10"/>
       <c r="H119" s="4"/>
@@ -2518,7 +2526,7 @@
       <c r="O119" s="10"/>
       <c r="P119" s="4"/>
     </row>
-    <row r="120" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="120" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D120" s="2"/>
       <c r="E120" s="10"/>
       <c r="H120" s="4"/>
@@ -2528,7 +2536,7 @@
       <c r="O120" s="10"/>
       <c r="P120" s="4"/>
     </row>
-    <row r="121" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="121" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D121" s="2"/>
       <c r="E121" s="10"/>
       <c r="H121" s="4"/>
@@ -2538,7 +2546,7 @@
       <c r="O121" s="10"/>
       <c r="P121" s="4"/>
     </row>
-    <row r="122" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="122" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D122" s="2"/>
       <c r="E122" s="10"/>
       <c r="H122" s="4"/>
@@ -2548,7 +2556,7 @@
       <c r="O122" s="10"/>
       <c r="P122" s="4"/>
     </row>
-    <row r="123" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="123" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D123" s="2"/>
       <c r="E123" s="10"/>
       <c r="H123" s="4"/>
@@ -2558,7 +2566,7 @@
       <c r="O123" s="10"/>
       <c r="P123" s="4"/>
     </row>
-    <row r="124" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="124" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D124" s="2"/>
       <c r="E124" s="10"/>
       <c r="H124" s="4"/>
@@ -2568,7 +2576,7 @@
       <c r="O124" s="10"/>
       <c r="P124" s="4"/>
     </row>
-    <row r="125" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="125" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D125" s="2"/>
       <c r="E125" s="10"/>
       <c r="H125" s="4"/>
@@ -2578,7 +2586,7 @@
       <c r="O125" s="10"/>
       <c r="P125" s="4"/>
     </row>
-    <row r="126" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="126" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D126" s="2"/>
       <c r="E126" s="10"/>
       <c r="H126" s="4"/>
@@ -2588,7 +2596,7 @@
       <c r="O126" s="10"/>
       <c r="P126" s="4"/>
     </row>
-    <row r="127" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="127" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D127" s="2"/>
       <c r="E127" s="10"/>
       <c r="H127" s="4"/>
@@ -2598,7 +2606,7 @@
       <c r="O127" s="10"/>
       <c r="P127" s="4"/>
     </row>
-    <row r="128" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="128" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D128" s="2"/>
       <c r="E128" s="10"/>
       <c r="H128" s="4"/>
@@ -2608,7 +2616,7 @@
       <c r="O128" s="10"/>
       <c r="P128" s="4"/>
     </row>
-    <row r="129" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="129" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D129" s="2"/>
       <c r="E129" s="10"/>
       <c r="H129" s="4"/>
@@ -2618,7 +2626,7 @@
       <c r="O129" s="10"/>
       <c r="P129" s="4"/>
     </row>
-    <row r="130" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="130" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D130" s="2"/>
       <c r="E130" s="10"/>
       <c r="H130" s="4"/>
@@ -2628,7 +2636,7 @@
       <c r="O130" s="10"/>
       <c r="P130" s="4"/>
     </row>
-    <row r="131" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="131" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D131" s="2"/>
       <c r="E131" s="10"/>
       <c r="H131" s="4"/>
@@ -2638,7 +2646,7 @@
       <c r="O131" s="10"/>
       <c r="P131" s="4"/>
     </row>
-    <row r="132" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="132" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D132" s="2"/>
       <c r="E132" s="10"/>
       <c r="H132" s="4"/>
@@ -2648,7 +2656,7 @@
       <c r="O132" s="10"/>
       <c r="P132" s="4"/>
     </row>
-    <row r="133" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="133" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D133" s="2"/>
       <c r="E133" s="10"/>
       <c r="H133" s="4"/>
@@ -2658,7 +2666,7 @@
       <c r="O133" s="10"/>
       <c r="P133" s="4"/>
     </row>
-    <row r="134" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="134" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D134" s="2"/>
       <c r="E134" s="10"/>
       <c r="H134" s="4"/>
@@ -2668,7 +2676,7 @@
       <c r="O134" s="10"/>
       <c r="P134" s="4"/>
     </row>
-    <row r="135" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="135" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D135" s="2"/>
       <c r="E135" s="10"/>
       <c r="H135" s="4"/>
@@ -2678,7 +2686,7 @@
       <c r="O135" s="10"/>
       <c r="P135" s="4"/>
     </row>
-    <row r="136" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="136" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D136" s="2"/>
       <c r="E136" s="10"/>
       <c r="H136" s="4"/>
@@ -2688,7 +2696,7 @@
       <c r="O136" s="10"/>
       <c r="P136" s="4"/>
     </row>
-    <row r="137" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="137" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D137" s="2"/>
       <c r="E137" s="10"/>
       <c r="H137" s="4"/>
@@ -2698,7 +2706,7 @@
       <c r="O137" s="10"/>
       <c r="P137" s="4"/>
     </row>
-    <row r="138" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="138" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D138" s="2"/>
       <c r="E138" s="10"/>
       <c r="H138" s="4"/>
@@ -2708,7 +2716,7 @@
       <c r="O138" s="10"/>
       <c r="P138" s="4"/>
     </row>
-    <row r="139" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="139" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D139" s="2"/>
       <c r="E139" s="10"/>
       <c r="H139" s="4"/>
@@ -2718,7 +2726,7 @@
       <c r="O139" s="10"/>
       <c r="P139" s="4"/>
     </row>
-    <row r="140" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="140" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D140" s="2"/>
       <c r="E140" s="10"/>
       <c r="H140" s="4"/>
@@ -2728,7 +2736,7 @@
       <c r="O140" s="10"/>
       <c r="P140" s="4"/>
     </row>
-    <row r="141" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="141" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D141" s="2"/>
       <c r="E141" s="10"/>
       <c r="H141" s="4"/>
@@ -2738,7 +2746,7 @@
       <c r="O141" s="10"/>
       <c r="P141" s="4"/>
     </row>
-    <row r="142" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="142" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D142" s="2"/>
       <c r="E142" s="10"/>
       <c r="H142" s="4"/>
@@ -2748,7 +2756,7 @@
       <c r="O142" s="10"/>
       <c r="P142" s="4"/>
     </row>
-    <row r="143" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="143" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D143" s="2"/>
       <c r="E143" s="10"/>
       <c r="H143" s="4"/>
@@ -2758,7 +2766,7 @@
       <c r="O143" s="10"/>
       <c r="P143" s="4"/>
     </row>
-    <row r="144" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="144" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D144" s="2"/>
       <c r="E144" s="10"/>
       <c r="H144" s="4"/>
@@ -2768,7 +2776,7 @@
       <c r="O144" s="10"/>
       <c r="P144" s="4"/>
     </row>
-    <row r="145" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="145" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D145" s="2"/>
       <c r="E145" s="10"/>
       <c r="H145" s="4"/>
@@ -2778,7 +2786,7 @@
       <c r="O145" s="10"/>
       <c r="P145" s="4"/>
     </row>
-    <row r="146" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="146" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D146" s="2"/>
       <c r="E146" s="10"/>
       <c r="H146" s="4"/>
@@ -2788,7 +2796,7 @@
       <c r="O146" s="10"/>
       <c r="P146" s="4"/>
     </row>
-    <row r="147" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="147" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D147" s="2"/>
       <c r="E147" s="10"/>
       <c r="H147" s="4"/>
@@ -2798,7 +2806,7 @@
       <c r="O147" s="10"/>
       <c r="P147" s="4"/>
     </row>
-    <row r="148" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="148" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D148" s="2"/>
       <c r="E148" s="10"/>
       <c r="H148" s="4"/>
@@ -2808,7 +2816,7 @@
       <c r="O148" s="10"/>
       <c r="P148" s="4"/>
     </row>
-    <row r="149" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="149" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D149" s="2"/>
       <c r="E149" s="10"/>
       <c r="H149" s="4"/>
@@ -2818,7 +2826,7 @@
       <c r="O149" s="10"/>
       <c r="P149" s="4"/>
     </row>
-    <row r="150" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="150" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D150" s="2"/>
       <c r="E150" s="10"/>
       <c r="H150" s="4"/>
@@ -2828,7 +2836,7 @@
       <c r="O150" s="10"/>
       <c r="P150" s="4"/>
     </row>
-    <row r="151" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="151" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D151" s="2"/>
       <c r="E151" s="10"/>
       <c r="H151" s="4"/>
@@ -2838,7 +2846,7 @@
       <c r="O151" s="10"/>
       <c r="P151" s="4"/>
     </row>
-    <row r="152" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="152" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D152" s="2"/>
       <c r="E152" s="10"/>
       <c r="H152" s="4"/>
@@ -2848,7 +2856,7 @@
       <c r="O152" s="10"/>
       <c r="P152" s="4"/>
     </row>
-    <row r="153" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="153" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D153" s="2"/>
       <c r="E153" s="10"/>
       <c r="H153" s="4"/>
@@ -2858,7 +2866,7 @@
       <c r="O153" s="10"/>
       <c r="P153" s="4"/>
     </row>
-    <row r="154" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="154" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D154" s="2"/>
       <c r="E154" s="10"/>
       <c r="H154" s="4"/>
@@ -2868,7 +2876,7 @@
       <c r="O154" s="10"/>
       <c r="P154" s="4"/>
     </row>
-    <row r="155" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="155" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D155" s="2"/>
       <c r="E155" s="10"/>
       <c r="H155" s="4"/>
@@ -2878,7 +2886,7 @@
       <c r="O155" s="10"/>
       <c r="P155" s="4"/>
     </row>
-    <row r="156" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="156" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D156" s="2"/>
       <c r="E156" s="10"/>
       <c r="H156" s="4"/>
@@ -2888,7 +2896,7 @@
       <c r="O156" s="10"/>
       <c r="P156" s="4"/>
     </row>
-    <row r="157" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="157" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D157" s="2"/>
       <c r="E157" s="10"/>
       <c r="H157" s="4"/>
@@ -2898,7 +2906,7 @@
       <c r="O157" s="10"/>
       <c r="P157" s="4"/>
     </row>
-    <row r="158" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="158" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D158" s="2"/>
       <c r="E158" s="10"/>
       <c r="H158" s="4"/>
@@ -2908,7 +2916,7 @@
       <c r="O158" s="10"/>
       <c r="P158" s="4"/>
     </row>
-    <row r="159" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="159" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D159" s="2"/>
       <c r="E159" s="10"/>
       <c r="H159" s="4"/>
@@ -2918,7 +2926,7 @@
       <c r="O159" s="10"/>
       <c r="P159" s="4"/>
     </row>
-    <row r="160" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="160" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D160" s="2"/>
       <c r="E160" s="10"/>
       <c r="H160" s="4"/>
@@ -2928,7 +2936,7 @@
       <c r="O160" s="10"/>
       <c r="P160" s="4"/>
     </row>
-    <row r="161" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="161" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D161" s="2"/>
       <c r="E161" s="10"/>
       <c r="H161" s="4"/>
@@ -2938,7 +2946,7 @@
       <c r="O161" s="10"/>
       <c r="P161" s="4"/>
     </row>
-    <row r="162" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="162" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D162" s="2"/>
       <c r="E162" s="10"/>
       <c r="H162" s="4"/>
@@ -2948,7 +2956,7 @@
       <c r="O162" s="10"/>
       <c r="P162" s="4"/>
     </row>
-    <row r="163" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="163" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D163" s="2"/>
       <c r="E163" s="10"/>
       <c r="H163" s="4"/>
@@ -2958,7 +2966,7 @@
       <c r="O163" s="10"/>
       <c r="P163" s="4"/>
     </row>
-    <row r="164" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="164" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D164" s="2"/>
       <c r="E164" s="10"/>
       <c r="H164" s="4"/>
@@ -2968,7 +2976,7 @@
       <c r="O164" s="10"/>
       <c r="P164" s="4"/>
     </row>
-    <row r="165" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="165" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D165" s="2"/>
       <c r="E165" s="10"/>
       <c r="H165" s="4"/>
@@ -2978,7 +2986,7 @@
       <c r="O165" s="10"/>
       <c r="P165" s="4"/>
     </row>
-    <row r="166" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="166" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D166" s="2"/>
       <c r="E166" s="10"/>
       <c r="H166" s="4"/>
@@ -2988,7 +2996,7 @@
       <c r="O166" s="10"/>
       <c r="P166" s="4"/>
     </row>
-    <row r="167" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="167" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D167" s="2"/>
       <c r="E167" s="10"/>
       <c r="H167" s="4"/>
@@ -2998,7 +3006,7 @@
       <c r="O167" s="10"/>
       <c r="P167" s="4"/>
     </row>
-    <row r="168" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="168" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D168" s="2"/>
       <c r="E168" s="10"/>
       <c r="H168" s="4"/>
@@ -3008,7 +3016,7 @@
       <c r="O168" s="10"/>
       <c r="P168" s="4"/>
     </row>
-    <row r="169" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="169" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D169" s="2"/>
       <c r="E169" s="10"/>
       <c r="H169" s="4"/>
@@ -3018,7 +3026,7 @@
       <c r="O169" s="10"/>
       <c r="P169" s="4"/>
     </row>
-    <row r="170" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="170" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D170" s="2"/>
       <c r="E170" s="10"/>
       <c r="H170" s="4"/>
@@ -3028,7 +3036,7 @@
       <c r="O170" s="10"/>
       <c r="P170" s="4"/>
     </row>
-    <row r="171" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="171" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D171" s="2"/>
       <c r="E171" s="10"/>
       <c r="H171" s="4"/>
@@ -3038,7 +3046,7 @@
       <c r="O171" s="10"/>
       <c r="P171" s="4"/>
     </row>
-    <row r="172" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="172" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D172" s="2"/>
       <c r="E172" s="10"/>
       <c r="H172" s="4"/>
@@ -3048,7 +3056,7 @@
       <c r="O172" s="10"/>
       <c r="P172" s="4"/>
     </row>
-    <row r="173" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="173" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D173" s="2"/>
       <c r="E173" s="10"/>
       <c r="H173" s="4"/>
@@ -3058,7 +3066,7 @@
       <c r="O173" s="10"/>
       <c r="P173" s="4"/>
     </row>
-    <row r="174" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="174" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D174" s="2"/>
       <c r="E174" s="10"/>
       <c r="H174" s="4"/>
@@ -3068,7 +3076,7 @@
       <c r="O174" s="10"/>
       <c r="P174" s="4"/>
     </row>
-    <row r="175" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="175" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D175" s="2"/>
       <c r="E175" s="10"/>
       <c r="H175" s="4"/>
@@ -3078,7 +3086,7 @@
       <c r="O175" s="10"/>
       <c r="P175" s="4"/>
     </row>
-    <row r="176" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="176" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D176" s="2"/>
       <c r="E176" s="10"/>
       <c r="H176" s="4"/>
@@ -3088,7 +3096,7 @@
       <c r="O176" s="10"/>
       <c r="P176" s="4"/>
     </row>
-    <row r="177" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="177" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D177" s="2"/>
       <c r="E177" s="10"/>
       <c r="H177" s="4"/>
@@ -3098,7 +3106,7 @@
       <c r="O177" s="10"/>
       <c r="P177" s="4"/>
     </row>
-    <row r="178" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="178" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D178" s="2"/>
       <c r="E178" s="10"/>
       <c r="H178" s="4"/>
@@ -3108,7 +3116,7 @@
       <c r="O178" s="10"/>
       <c r="P178" s="4"/>
     </row>
-    <row r="179" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="179" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D179" s="2"/>
       <c r="E179" s="10"/>
       <c r="H179" s="4"/>
@@ -3118,7 +3126,7 @@
       <c r="O179" s="10"/>
       <c r="P179" s="4"/>
     </row>
-    <row r="180" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="180" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D180" s="2"/>
       <c r="E180" s="10"/>
       <c r="H180" s="4"/>
@@ -3128,7 +3136,7 @@
       <c r="O180" s="10"/>
       <c r="P180" s="4"/>
     </row>
-    <row r="181" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="181" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D181" s="2"/>
       <c r="E181" s="10"/>
       <c r="H181" s="4"/>
@@ -3138,7 +3146,7 @@
       <c r="O181" s="10"/>
       <c r="P181" s="4"/>
     </row>
-    <row r="182" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="182" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D182" s="2"/>
       <c r="E182" s="10"/>
       <c r="H182" s="4"/>
@@ -3148,7 +3156,7 @@
       <c r="O182" s="10"/>
       <c r="P182" s="4"/>
     </row>
-    <row r="183" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="183" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D183" s="2"/>
       <c r="E183" s="10"/>
       <c r="H183" s="4"/>
@@ -3158,7 +3166,7 @@
       <c r="O183" s="10"/>
       <c r="P183" s="4"/>
     </row>
-    <row r="184" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="184" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D184" s="2"/>
       <c r="E184" s="10"/>
       <c r="H184" s="4"/>
@@ -3168,7 +3176,7 @@
       <c r="O184" s="10"/>
       <c r="P184" s="4"/>
     </row>
-    <row r="185" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="185" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D185" s="2"/>
       <c r="E185" s="10"/>
       <c r="H185" s="4"/>
@@ -3178,7 +3186,7 @@
       <c r="O185" s="10"/>
       <c r="P185" s="4"/>
     </row>
-    <row r="186" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="186" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D186" s="2"/>
       <c r="E186" s="10"/>
       <c r="H186" s="4"/>
@@ -3188,7 +3196,7 @@
       <c r="O186" s="10"/>
       <c r="P186" s="4"/>
     </row>
-    <row r="187" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="187" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D187" s="2"/>
       <c r="E187" s="10"/>
       <c r="H187" s="4"/>
@@ -3198,7 +3206,7 @@
       <c r="O187" s="10"/>
       <c r="P187" s="4"/>
     </row>
-    <row r="188" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="188" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D188" s="2"/>
       <c r="E188" s="10"/>
       <c r="H188" s="4"/>
@@ -3208,7 +3216,7 @@
       <c r="O188" s="10"/>
       <c r="P188" s="4"/>
     </row>
-    <row r="189" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="189" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D189" s="2"/>
       <c r="E189" s="10"/>
       <c r="H189" s="4"/>
@@ -3218,7 +3226,7 @@
       <c r="O189" s="10"/>
       <c r="P189" s="4"/>
     </row>
-    <row r="190" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="190" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D190" s="2"/>
       <c r="E190" s="10"/>
       <c r="H190" s="4"/>
@@ -3228,7 +3236,7 @@
       <c r="O190" s="10"/>
       <c r="P190" s="4"/>
     </row>
-    <row r="191" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="191" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D191" s="2"/>
       <c r="E191" s="10"/>
       <c r="H191" s="4"/>
@@ -3238,7 +3246,7 @@
       <c r="O191" s="10"/>
       <c r="P191" s="4"/>
     </row>
-    <row r="192" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="192" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D192" s="2"/>
       <c r="E192" s="10"/>
       <c r="H192" s="4"/>
@@ -3248,7 +3256,7 @@
       <c r="O192" s="10"/>
       <c r="P192" s="4"/>
     </row>
-    <row r="193" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="193" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D193" s="2"/>
       <c r="E193" s="10"/>
       <c r="H193" s="4"/>
@@ -3258,7 +3266,7 @@
       <c r="O193" s="10"/>
       <c r="P193" s="4"/>
     </row>
-    <row r="194" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="194" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D194" s="2"/>
       <c r="E194" s="10"/>
       <c r="H194" s="4"/>
@@ -3268,7 +3276,7 @@
       <c r="O194" s="10"/>
       <c r="P194" s="4"/>
     </row>
-    <row r="195" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="195" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D195" s="2"/>
       <c r="E195" s="10"/>
       <c r="H195" s="4"/>
@@ -3278,7 +3286,7 @@
       <c r="O195" s="10"/>
       <c r="P195" s="4"/>
     </row>
-    <row r="196" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="196" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D196" s="2"/>
       <c r="E196" s="10"/>
       <c r="H196" s="4"/>
@@ -3288,7 +3296,7 @@
       <c r="O196" s="10"/>
       <c r="P196" s="4"/>
     </row>
-    <row r="197" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="197" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D197" s="2"/>
       <c r="E197" s="10"/>
       <c r="H197" s="4"/>
@@ -3298,7 +3306,7 @@
       <c r="O197" s="10"/>
       <c r="P197" s="4"/>
     </row>
-    <row r="198" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="198" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D198" s="2"/>
       <c r="E198" s="10"/>
       <c r="H198" s="4"/>
@@ -3308,7 +3316,7 @@
       <c r="O198" s="10"/>
       <c r="P198" s="4"/>
     </row>
-    <row r="199" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="199" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D199" s="2"/>
       <c r="E199" s="10"/>
       <c r="H199" s="4"/>
@@ -3318,7 +3326,7 @@
       <c r="O199" s="10"/>
       <c r="P199" s="4"/>
     </row>
-    <row r="200" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="200" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D200" s="2"/>
       <c r="E200" s="10"/>
       <c r="H200" s="4"/>
@@ -3328,7 +3336,7 @@
       <c r="O200" s="10"/>
       <c r="P200" s="4"/>
     </row>
-    <row r="201" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="201" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D201" s="2"/>
       <c r="E201" s="10"/>
       <c r="H201" s="4"/>
@@ -3338,7 +3346,7 @@
       <c r="O201" s="10"/>
       <c r="P201" s="4"/>
     </row>
-    <row r="202" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="202" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D202" s="2"/>
       <c r="E202" s="10"/>
       <c r="H202" s="4"/>
@@ -3348,7 +3356,7 @@
       <c r="O202" s="10"/>
       <c r="P202" s="4"/>
     </row>
-    <row r="203" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="203" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D203" s="2"/>
       <c r="E203" s="10"/>
       <c r="H203" s="4"/>
@@ -3358,7 +3366,7 @@
       <c r="O203" s="10"/>
       <c r="P203" s="4"/>
     </row>
-    <row r="204" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="204" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D204" s="2"/>
       <c r="E204" s="10"/>
       <c r="H204" s="4"/>
@@ -3368,7 +3376,7 @@
       <c r="O204" s="10"/>
       <c r="P204" s="4"/>
     </row>
-    <row r="205" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="205" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D205" s="2"/>
       <c r="E205" s="10"/>
       <c r="H205" s="4"/>
@@ -3378,7 +3386,7 @@
       <c r="O205" s="10"/>
       <c r="P205" s="4"/>
     </row>
-    <row r="206" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="206" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D206" s="2"/>
       <c r="E206" s="10"/>
       <c r="H206" s="4"/>
@@ -3388,7 +3396,7 @@
       <c r="O206" s="10"/>
       <c r="P206" s="4"/>
     </row>
-    <row r="207" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="207" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D207" s="2"/>
       <c r="E207" s="10"/>
       <c r="H207" s="4"/>
@@ -3398,7 +3406,7 @@
       <c r="O207" s="10"/>
       <c r="P207" s="4"/>
     </row>
-    <row r="208" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="208" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D208" s="2"/>
       <c r="E208" s="10"/>
       <c r="H208" s="4"/>
@@ -3408,7 +3416,7 @@
       <c r="O208" s="10"/>
       <c r="P208" s="4"/>
     </row>
-    <row r="209" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="209" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D209" s="2"/>
       <c r="E209" s="10"/>
       <c r="H209" s="4"/>
@@ -3418,7 +3426,7 @@
       <c r="O209" s="10"/>
       <c r="P209" s="4"/>
     </row>
-    <row r="210" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="210" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D210" s="2"/>
       <c r="E210" s="10"/>
       <c r="H210" s="4"/>
@@ -3428,7 +3436,7 @@
       <c r="O210" s="10"/>
       <c r="P210" s="4"/>
     </row>
-    <row r="211" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="211" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D211" s="2"/>
       <c r="E211" s="10"/>
       <c r="H211" s="4"/>
@@ -3438,7 +3446,7 @@
       <c r="O211" s="10"/>
       <c r="P211" s="4"/>
     </row>
-    <row r="212" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="212" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D212" s="2"/>
       <c r="E212" s="10"/>
       <c r="H212" s="4"/>
@@ -3448,7 +3456,7 @@
       <c r="O212" s="10"/>
       <c r="P212" s="4"/>
     </row>
-    <row r="213" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="213" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D213" s="2"/>
       <c r="E213" s="10"/>
       <c r="H213" s="4"/>
@@ -3458,7 +3466,7 @@
       <c r="O213" s="10"/>
       <c r="P213" s="4"/>
     </row>
-    <row r="214" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="214" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D214" s="2"/>
       <c r="E214" s="10"/>
       <c r="H214" s="4"/>
@@ -3468,7 +3476,7 @@
       <c r="O214" s="10"/>
       <c r="P214" s="4"/>
     </row>
-    <row r="215" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="215" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D215" s="2"/>
       <c r="E215" s="10"/>
       <c r="H215" s="4"/>
@@ -3478,7 +3486,7 @@
       <c r="O215" s="10"/>
       <c r="P215" s="4"/>
     </row>
-    <row r="216" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="216" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D216" s="2"/>
       <c r="E216" s="10"/>
       <c r="H216" s="4"/>
@@ -3488,7 +3496,7 @@
       <c r="O216" s="10"/>
       <c r="P216" s="4"/>
     </row>
-    <row r="217" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="217" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D217" s="2"/>
       <c r="E217" s="10"/>
       <c r="H217" s="4"/>
@@ -3498,7 +3506,7 @@
       <c r="O217" s="10"/>
       <c r="P217" s="4"/>
     </row>
-    <row r="218" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="218" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D218" s="2"/>
       <c r="E218" s="10"/>
       <c r="H218" s="4"/>
@@ -3508,7 +3516,7 @@
       <c r="O218" s="10"/>
       <c r="P218" s="4"/>
     </row>
-    <row r="219" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="219" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D219" s="2"/>
       <c r="E219" s="10"/>
       <c r="H219" s="4"/>
@@ -3518,7 +3526,7 @@
       <c r="O219" s="10"/>
       <c r="P219" s="4"/>
     </row>
-    <row r="220" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="220" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D220" s="2"/>
       <c r="E220" s="10"/>
       <c r="H220" s="4"/>
@@ -3528,7 +3536,7 @@
       <c r="O220" s="10"/>
       <c r="P220" s="4"/>
     </row>
-    <row r="221" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="221" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D221" s="2"/>
       <c r="E221" s="10"/>
       <c r="H221" s="4"/>
@@ -3538,7 +3546,7 @@
       <c r="O221" s="10"/>
       <c r="P221" s="4"/>
     </row>
-    <row r="222" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="222" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D222" s="2"/>
       <c r="E222" s="10"/>
       <c r="H222" s="4"/>
@@ -3548,7 +3556,7 @@
       <c r="O222" s="10"/>
       <c r="P222" s="4"/>
     </row>
-    <row r="223" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="223" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D223" s="2"/>
       <c r="E223" s="10"/>
       <c r="H223" s="4"/>
@@ -3558,7 +3566,7 @@
       <c r="O223" s="10"/>
       <c r="P223" s="4"/>
     </row>
-    <row r="224" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="224" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D224" s="2"/>
       <c r="E224" s="10"/>
       <c r="H224" s="4"/>
@@ -3568,7 +3576,7 @@
       <c r="O224" s="10"/>
       <c r="P224" s="4"/>
     </row>
-    <row r="225" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="225" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D225" s="2"/>
       <c r="E225" s="10"/>
       <c r="H225" s="4"/>
@@ -3578,7 +3586,7 @@
       <c r="O225" s="10"/>
       <c r="P225" s="4"/>
     </row>
-    <row r="226" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="226" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D226" s="2"/>
       <c r="E226" s="10"/>
       <c r="H226" s="4"/>
@@ -3588,7 +3596,7 @@
       <c r="O226" s="10"/>
       <c r="P226" s="4"/>
     </row>
-    <row r="227" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="227" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D227" s="2"/>
       <c r="E227" s="10"/>
       <c r="H227" s="4"/>
@@ -3598,7 +3606,7 @@
       <c r="O227" s="10"/>
       <c r="P227" s="4"/>
     </row>
-    <row r="228" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="228" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D228" s="2"/>
       <c r="E228" s="10"/>
       <c r="H228" s="4"/>
@@ -3608,7 +3616,7 @@
       <c r="O228" s="10"/>
       <c r="P228" s="4"/>
     </row>
-    <row r="229" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="229" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D229" s="2"/>
       <c r="E229" s="10"/>
       <c r="H229" s="4"/>
@@ -3618,7 +3626,7 @@
       <c r="O229" s="10"/>
       <c r="P229" s="4"/>
     </row>
-    <row r="230" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="230" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D230" s="2"/>
       <c r="E230" s="10"/>
       <c r="H230" s="4"/>
@@ -3628,7 +3636,7 @@
       <c r="O230" s="10"/>
       <c r="P230" s="4"/>
     </row>
-    <row r="231" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="231" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D231" s="2"/>
       <c r="E231" s="10"/>
       <c r="H231" s="4"/>
@@ -3638,7 +3646,7 @@
       <c r="O231" s="10"/>
       <c r="P231" s="4"/>
     </row>
-    <row r="232" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="232" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D232" s="2"/>
       <c r="E232" s="10"/>
       <c r="H232" s="4"/>
@@ -3648,7 +3656,7 @@
       <c r="O232" s="10"/>
       <c r="P232" s="4"/>
     </row>
-    <row r="233" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="233" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D233" s="2"/>
       <c r="E233" s="10"/>
       <c r="H233" s="4"/>
@@ -3658,7 +3666,7 @@
       <c r="O233" s="10"/>
       <c r="P233" s="4"/>
     </row>
-    <row r="234" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="234" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D234" s="2"/>
       <c r="E234" s="10"/>
       <c r="H234" s="4"/>
@@ -3668,7 +3676,7 @@
       <c r="O234" s="10"/>
       <c r="P234" s="4"/>
     </row>
-    <row r="235" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="235" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D235" s="2"/>
       <c r="E235" s="10"/>
       <c r="H235" s="4"/>
@@ -3678,7 +3686,7 @@
       <c r="O235" s="10"/>
       <c r="P235" s="4"/>
     </row>
-    <row r="236" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="236" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D236" s="2"/>
       <c r="E236" s="10"/>
       <c r="H236" s="4"/>
@@ -3688,7 +3696,7 @@
       <c r="O236" s="10"/>
       <c r="P236" s="4"/>
     </row>
-    <row r="237" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="237" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D237" s="2"/>
       <c r="E237" s="10"/>
       <c r="H237" s="4"/>
@@ -3698,7 +3706,7 @@
       <c r="O237" s="10"/>
       <c r="P237" s="4"/>
     </row>
-    <row r="238" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="238" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D238" s="2"/>
       <c r="E238" s="10"/>
       <c r="H238" s="4"/>
@@ -3708,7 +3716,7 @@
       <c r="O238" s="10"/>
       <c r="P238" s="4"/>
     </row>
-    <row r="239" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="239" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D239" s="2"/>
       <c r="E239" s="10"/>
       <c r="H239" s="4"/>
@@ -3718,7 +3726,7 @@
       <c r="O239" s="10"/>
       <c r="P239" s="4"/>
     </row>
-    <row r="240" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="240" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D240" s="2"/>
       <c r="E240" s="10"/>
       <c r="H240" s="4"/>
@@ -3728,7 +3736,7 @@
       <c r="O240" s="10"/>
       <c r="P240" s="4"/>
     </row>
-    <row r="241" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="241" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D241" s="2"/>
       <c r="E241" s="10"/>
       <c r="H241" s="4"/>
@@ -3738,7 +3746,7 @@
       <c r="O241" s="10"/>
       <c r="P241" s="4"/>
     </row>
-    <row r="242" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="242" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D242" s="2"/>
       <c r="E242" s="10"/>
       <c r="H242" s="4"/>
@@ -3748,7 +3756,7 @@
       <c r="O242" s="10"/>
       <c r="P242" s="4"/>
     </row>
-    <row r="243" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="243" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D243" s="2"/>
       <c r="E243" s="10"/>
       <c r="H243" s="4"/>
@@ -3758,7 +3766,7 @@
       <c r="O243" s="10"/>
       <c r="P243" s="4"/>
     </row>
-    <row r="244" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="244" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D244" s="2"/>
       <c r="E244" s="10"/>
       <c r="H244" s="4"/>
@@ -3768,7 +3776,7 @@
       <c r="O244" s="10"/>
       <c r="P244" s="4"/>
     </row>
-    <row r="245" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="245" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D245" s="2"/>
       <c r="E245" s="10"/>
       <c r="H245" s="4"/>
@@ -3778,7 +3786,7 @@
       <c r="O245" s="10"/>
       <c r="P245" s="4"/>
     </row>
-    <row r="246" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="246" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D246" s="2"/>
       <c r="E246" s="10"/>
       <c r="H246" s="4"/>
@@ -3788,7 +3796,7 @@
       <c r="O246" s="10"/>
       <c r="P246" s="4"/>
     </row>
-    <row r="247" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="247" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D247" s="2"/>
       <c r="E247" s="10"/>
       <c r="H247" s="4"/>
@@ -3798,7 +3806,7 @@
       <c r="O247" s="10"/>
       <c r="P247" s="4"/>
     </row>
-    <row r="248" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="248" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D248" s="2"/>
       <c r="E248" s="10"/>
       <c r="H248" s="4"/>
@@ -3808,7 +3816,7 @@
       <c r="O248" s="10"/>
       <c r="P248" s="4"/>
     </row>
-    <row r="249" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="249" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D249" s="2"/>
       <c r="E249" s="10"/>
       <c r="H249" s="4"/>
@@ -3818,7 +3826,7 @@
       <c r="O249" s="10"/>
       <c r="P249" s="4"/>
     </row>
-    <row r="250" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="250" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D250" s="2"/>
       <c r="E250" s="10"/>
       <c r="H250" s="4"/>
@@ -3828,7 +3836,7 @@
       <c r="O250" s="10"/>
       <c r="P250" s="4"/>
     </row>
-    <row r="251" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="251" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D251" s="2"/>
       <c r="E251" s="10"/>
       <c r="H251" s="4"/>
@@ -3838,7 +3846,7 @@
       <c r="O251" s="10"/>
       <c r="P251" s="4"/>
     </row>
-    <row r="252" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="252" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D252" s="2"/>
       <c r="E252" s="10"/>
       <c r="H252" s="4"/>
@@ -3848,7 +3856,7 @@
       <c r="O252" s="10"/>
       <c r="P252" s="4"/>
     </row>
-    <row r="253" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="253" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D253" s="2"/>
       <c r="E253" s="10"/>
       <c r="H253" s="4"/>
@@ -3858,7 +3866,7 @@
       <c r="O253" s="10"/>
       <c r="P253" s="4"/>
     </row>
-    <row r="254" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="254" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D254" s="2"/>
       <c r="E254" s="10"/>
       <c r="H254" s="4"/>
@@ -3868,7 +3876,7 @@
       <c r="O254" s="10"/>
       <c r="P254" s="4"/>
     </row>
-    <row r="255" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="255" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D255" s="2"/>
       <c r="E255" s="10"/>
       <c r="H255" s="4"/>
@@ -3878,7 +3886,7 @@
       <c r="O255" s="10"/>
       <c r="P255" s="4"/>
     </row>
-    <row r="256" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="256" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D256" s="2"/>
       <c r="E256" s="10"/>
       <c r="H256" s="4"/>
@@ -3888,7 +3896,7 @@
       <c r="O256" s="10"/>
       <c r="P256" s="4"/>
     </row>
-    <row r="257" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="257" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D257" s="2"/>
       <c r="E257" s="10"/>
       <c r="H257" s="4"/>
@@ -3898,7 +3906,7 @@
       <c r="O257" s="10"/>
       <c r="P257" s="4"/>
     </row>
-    <row r="258" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="258" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D258" s="2"/>
       <c r="E258" s="10"/>
       <c r="H258" s="4"/>
@@ -3908,7 +3916,7 @@
       <c r="O258" s="10"/>
       <c r="P258" s="4"/>
     </row>
-    <row r="259" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="259" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D259" s="2"/>
       <c r="E259" s="10"/>
       <c r="H259" s="4"/>
@@ -3918,7 +3926,7 @@
       <c r="O259" s="10"/>
       <c r="P259" s="4"/>
     </row>
-    <row r="260" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="260" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D260" s="2"/>
       <c r="E260" s="10"/>
       <c r="H260" s="4"/>
@@ -3928,7 +3936,7 @@
       <c r="O260" s="10"/>
       <c r="P260" s="4"/>
     </row>
-    <row r="261" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="261" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D261" s="2"/>
       <c r="E261" s="10"/>
       <c r="H261" s="4"/>
@@ -3938,7 +3946,7 @@
       <c r="O261" s="10"/>
       <c r="P261" s="4"/>
     </row>
-    <row r="262" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="262" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D262" s="2"/>
       <c r="E262" s="10"/>
       <c r="H262" s="4"/>
@@ -3948,7 +3956,7 @@
       <c r="O262" s="10"/>
       <c r="P262" s="4"/>
     </row>
-    <row r="263" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="263" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D263" s="2"/>
       <c r="E263" s="10"/>
       <c r="H263" s="4"/>
@@ -3958,7 +3966,7 @@
       <c r="O263" s="10"/>
       <c r="P263" s="4"/>
     </row>
-    <row r="264" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="264" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D264" s="2"/>
       <c r="E264" s="10"/>
       <c r="H264" s="4"/>
@@ -3968,7 +3976,7 @@
       <c r="O264" s="10"/>
       <c r="P264" s="4"/>
     </row>
-    <row r="265" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="265" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D265" s="2"/>
       <c r="E265" s="10"/>
       <c r="H265" s="4"/>
@@ -3978,7 +3986,7 @@
       <c r="O265" s="10"/>
       <c r="P265" s="4"/>
     </row>
-    <row r="266" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="266" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D266" s="2"/>
       <c r="E266" s="10"/>
       <c r="H266" s="4"/>
@@ -3988,7 +3996,7 @@
       <c r="O266" s="10"/>
       <c r="P266" s="4"/>
     </row>
-    <row r="267" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="267" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D267" s="2"/>
       <c r="E267" s="10"/>
       <c r="H267" s="4"/>
@@ -3998,7 +4006,7 @@
       <c r="O267" s="10"/>
       <c r="P267" s="4"/>
     </row>
-    <row r="268" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="268" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D268" s="2"/>
       <c r="E268" s="10"/>
       <c r="H268" s="4"/>
@@ -4008,7 +4016,7 @@
       <c r="O268" s="10"/>
       <c r="P268" s="4"/>
     </row>
-    <row r="269" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="269" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D269" s="2"/>
       <c r="E269" s="10"/>
       <c r="H269" s="4"/>
@@ -4018,7 +4026,7 @@
       <c r="O269" s="10"/>
       <c r="P269" s="4"/>
     </row>
-    <row r="270" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="270" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D270" s="2"/>
       <c r="E270" s="10"/>
       <c r="H270" s="4"/>
@@ -4028,7 +4036,7 @@
       <c r="O270" s="10"/>
       <c r="P270" s="4"/>
     </row>
-    <row r="271" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="271" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D271" s="2"/>
       <c r="E271" s="10"/>
       <c r="H271" s="4"/>
@@ -4038,7 +4046,7 @@
       <c r="O271" s="10"/>
       <c r="P271" s="4"/>
     </row>
-    <row r="272" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="272" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D272" s="2"/>
       <c r="E272" s="10"/>
       <c r="H272" s="4"/>
@@ -4048,7 +4056,7 @@
       <c r="O272" s="10"/>
       <c r="P272" s="4"/>
     </row>
-    <row r="273" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="273" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D273" s="2"/>
       <c r="E273" s="10"/>
       <c r="H273" s="4"/>
@@ -4058,7 +4066,7 @@
       <c r="O273" s="10"/>
       <c r="P273" s="4"/>
     </row>
-    <row r="274" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="274" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D274" s="2"/>
       <c r="E274" s="10"/>
       <c r="H274" s="4"/>
@@ -4068,7 +4076,7 @@
       <c r="O274" s="10"/>
       <c r="P274" s="4"/>
     </row>
-    <row r="275" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="275" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D275" s="2"/>
       <c r="E275" s="10"/>
       <c r="H275" s="4"/>
@@ -4078,7 +4086,7 @@
       <c r="O275" s="10"/>
       <c r="P275" s="4"/>
     </row>
-    <row r="276" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="276" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D276" s="2"/>
       <c r="E276" s="10"/>
       <c r="H276" s="4"/>
@@ -4088,7 +4096,7 @@
       <c r="O276" s="10"/>
       <c r="P276" s="4"/>
     </row>
-    <row r="277" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="277" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D277" s="2"/>
       <c r="E277" s="10"/>
       <c r="H277" s="4"/>
@@ -4098,7 +4106,7 @@
       <c r="O277" s="10"/>
       <c r="P277" s="4"/>
     </row>
-    <row r="278" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="278" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D278" s="2"/>
       <c r="E278" s="10"/>
       <c r="H278" s="4"/>
@@ -4108,7 +4116,7 @@
       <c r="O278" s="10"/>
       <c r="P278" s="4"/>
     </row>
-    <row r="279" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="279" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D279" s="2"/>
       <c r="E279" s="10"/>
       <c r="H279" s="4"/>
@@ -4118,7 +4126,7 @@
       <c r="O279" s="10"/>
       <c r="P279" s="4"/>
     </row>
-    <row r="280" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="280" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D280" s="2"/>
       <c r="E280" s="10"/>
       <c r="H280" s="4"/>
@@ -4128,7 +4136,7 @@
       <c r="O280" s="10"/>
       <c r="P280" s="4"/>
     </row>
-    <row r="281" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="281" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D281" s="2"/>
       <c r="E281" s="10"/>
       <c r="H281" s="4"/>
@@ -4138,7 +4146,7 @@
       <c r="O281" s="10"/>
       <c r="P281" s="4"/>
     </row>
-    <row r="282" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="282" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D282" s="2"/>
       <c r="E282" s="10"/>
       <c r="H282" s="4"/>
@@ -4148,7 +4156,7 @@
       <c r="O282" s="10"/>
       <c r="P282" s="4"/>
     </row>
-    <row r="283" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="283" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D283" s="2"/>
       <c r="E283" s="10"/>
       <c r="H283" s="4"/>
@@ -4158,7 +4166,7 @@
       <c r="O283" s="10"/>
       <c r="P283" s="4"/>
     </row>
-    <row r="284" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="284" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D284" s="2"/>
       <c r="E284" s="10"/>
       <c r="H284" s="4"/>
@@ -4168,7 +4176,7 @@
       <c r="O284" s="10"/>
       <c r="P284" s="4"/>
     </row>
-    <row r="285" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="285" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D285" s="2"/>
       <c r="E285" s="10"/>
       <c r="H285" s="4"/>
@@ -4178,7 +4186,7 @@
       <c r="O285" s="10"/>
       <c r="P285" s="4"/>
     </row>
-    <row r="286" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="286" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D286" s="2"/>
       <c r="E286" s="10"/>
       <c r="H286" s="4"/>
@@ -4188,7 +4196,7 @@
       <c r="O286" s="10"/>
       <c r="P286" s="4"/>
     </row>
-    <row r="287" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="287" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D287" s="2"/>
       <c r="E287" s="10"/>
       <c r="H287" s="4"/>
@@ -4198,7 +4206,7 @@
       <c r="O287" s="10"/>
       <c r="P287" s="4"/>
     </row>
-    <row r="288" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="288" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D288" s="2"/>
       <c r="E288" s="10"/>
       <c r="H288" s="4"/>
@@ -4208,7 +4216,7 @@
       <c r="O288" s="10"/>
       <c r="P288" s="4"/>
     </row>
-    <row r="289" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="289" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D289" s="2"/>
       <c r="E289" s="10"/>
       <c r="H289" s="4"/>
@@ -4218,7 +4226,7 @@
       <c r="O289" s="10"/>
       <c r="P289" s="4"/>
     </row>
-    <row r="290" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="290" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D290" s="2"/>
       <c r="E290" s="10"/>
       <c r="H290" s="4"/>
@@ -4228,7 +4236,7 @@
       <c r="O290" s="10"/>
       <c r="P290" s="4"/>
     </row>
-    <row r="291" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="291" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D291" s="2"/>
       <c r="E291" s="10"/>
       <c r="H291" s="4"/>
@@ -4238,7 +4246,7 @@
       <c r="O291" s="10"/>
       <c r="P291" s="4"/>
     </row>
-    <row r="292" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="292" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D292" s="2"/>
       <c r="E292" s="10"/>
       <c r="H292" s="4"/>
@@ -4248,7 +4256,7 @@
       <c r="O292" s="10"/>
       <c r="P292" s="4"/>
     </row>
-    <row r="293" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="293" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D293" s="2"/>
       <c r="E293" s="10"/>
       <c r="H293" s="4"/>
@@ -4258,7 +4266,7 @@
       <c r="O293" s="10"/>
       <c r="P293" s="4"/>
     </row>
-    <row r="294" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="294" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D294" s="2"/>
       <c r="E294" s="10"/>
       <c r="H294" s="4"/>
@@ -4268,7 +4276,7 @@
       <c r="O294" s="10"/>
       <c r="P294" s="4"/>
     </row>
-    <row r="295" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="295" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D295" s="2"/>
       <c r="E295" s="10"/>
       <c r="H295" s="4"/>
@@ -4278,7 +4286,7 @@
       <c r="O295" s="10"/>
       <c r="P295" s="4"/>
     </row>
-    <row r="296" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="296" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D296" s="2"/>
       <c r="E296" s="10"/>
       <c r="H296" s="4"/>
@@ -4288,7 +4296,7 @@
       <c r="O296" s="10"/>
       <c r="P296" s="4"/>
     </row>
-    <row r="297" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="297" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D297" s="2"/>
       <c r="E297" s="10"/>
       <c r="H297" s="4"/>
@@ -4298,7 +4306,7 @@
       <c r="O297" s="10"/>
       <c r="P297" s="4"/>
     </row>
-    <row r="298" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="298" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D298" s="2"/>
       <c r="E298" s="10"/>
       <c r="H298" s="4"/>
@@ -4308,7 +4316,7 @@
       <c r="O298" s="10"/>
       <c r="P298" s="4"/>
     </row>
-    <row r="299" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="299" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D299" s="2"/>
       <c r="E299" s="10"/>
       <c r="H299" s="4"/>
@@ -4318,7 +4326,7 @@
       <c r="O299" s="10"/>
       <c r="P299" s="4"/>
     </row>
-    <row r="300" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="300" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D300" s="2"/>
       <c r="E300" s="10"/>
       <c r="H300" s="4"/>
@@ -4328,7 +4336,7 @@
       <c r="O300" s="10"/>
       <c r="P300" s="4"/>
     </row>
-    <row r="301" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="301" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D301" s="2"/>
       <c r="E301" s="10"/>
       <c r="H301" s="4"/>
@@ -4338,7 +4346,7 @@
       <c r="O301" s="10"/>
       <c r="P301" s="4"/>
     </row>
-    <row r="302" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="302" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D302" s="2"/>
       <c r="E302" s="10"/>
       <c r="H302" s="4"/>
@@ -4348,7 +4356,7 @@
       <c r="O302" s="10"/>
       <c r="P302" s="4"/>
     </row>
-    <row r="303" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="303" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D303" s="2"/>
       <c r="E303" s="10"/>
       <c r="H303" s="4"/>
@@ -4358,7 +4366,7 @@
       <c r="O303" s="10"/>
       <c r="P303" s="4"/>
     </row>
-    <row r="304" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="304" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D304" s="2"/>
       <c r="E304" s="10"/>
       <c r="H304" s="4"/>
@@ -4368,7 +4376,7 @@
       <c r="O304" s="10"/>
       <c r="P304" s="4"/>
     </row>
-    <row r="305" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="305" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D305" s="2"/>
       <c r="E305" s="10"/>
       <c r="H305" s="4"/>
@@ -4378,7 +4386,7 @@
       <c r="O305" s="10"/>
       <c r="P305" s="4"/>
     </row>
-    <row r="306" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="306" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D306" s="2"/>
       <c r="E306" s="10"/>
       <c r="H306" s="4"/>
@@ -4388,7 +4396,7 @@
       <c r="O306" s="10"/>
       <c r="P306" s="4"/>
     </row>
-    <row r="307" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="307" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D307" s="2"/>
       <c r="E307" s="10"/>
       <c r="H307" s="4"/>
@@ -4398,7 +4406,7 @@
       <c r="O307" s="10"/>
       <c r="P307" s="4"/>
     </row>
-    <row r="308" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="308" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D308" s="2"/>
       <c r="E308" s="10"/>
       <c r="H308" s="4"/>
@@ -4408,7 +4416,7 @@
       <c r="O308" s="10"/>
       <c r="P308" s="4"/>
     </row>
-    <row r="309" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="309" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D309" s="2"/>
       <c r="E309" s="10"/>
       <c r="H309" s="4"/>
@@ -4418,7 +4426,7 @@
       <c r="O309" s="10"/>
       <c r="P309" s="4"/>
     </row>
-    <row r="310" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="310" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D310" s="2"/>
       <c r="E310" s="10"/>
       <c r="H310" s="4"/>
@@ -4428,7 +4436,7 @@
       <c r="O310" s="10"/>
       <c r="P310" s="4"/>
     </row>
-    <row r="311" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="311" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D311" s="2"/>
       <c r="E311" s="10"/>
       <c r="H311" s="4"/>
@@ -4438,7 +4446,7 @@
       <c r="O311" s="10"/>
       <c r="P311" s="4"/>
     </row>
-    <row r="312" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="312" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D312" s="2"/>
       <c r="E312" s="10"/>
       <c r="H312" s="4"/>
@@ -4448,7 +4456,7 @@
       <c r="O312" s="10"/>
       <c r="P312" s="4"/>
     </row>
-    <row r="313" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="313" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D313" s="2"/>
       <c r="E313" s="10"/>
       <c r="H313" s="4"/>
@@ -4458,7 +4466,7 @@
       <c r="O313" s="10"/>
       <c r="P313" s="4"/>
     </row>
-    <row r="314" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="314" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D314" s="2"/>
       <c r="E314" s="10"/>
       <c r="H314" s="4"/>
@@ -4468,7 +4476,7 @@
       <c r="O314" s="10"/>
       <c r="P314" s="4"/>
     </row>
-    <row r="315" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="315" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D315" s="2"/>
       <c r="E315" s="10"/>
       <c r="H315" s="4"/>
@@ -4478,7 +4486,7 @@
       <c r="O315" s="10"/>
       <c r="P315" s="4"/>
     </row>
-    <row r="316" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="316" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D316" s="2"/>
       <c r="E316" s="10"/>
       <c r="H316" s="4"/>
@@ -4488,7 +4496,7 @@
       <c r="O316" s="10"/>
       <c r="P316" s="4"/>
     </row>
-    <row r="317" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="317" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D317" s="2"/>
       <c r="E317" s="10"/>
       <c r="H317" s="4"/>
@@ -4498,7 +4506,7 @@
       <c r="O317" s="10"/>
       <c r="P317" s="4"/>
     </row>
-    <row r="318" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="318" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D318" s="2"/>
       <c r="E318" s="10"/>
       <c r="H318" s="4"/>
@@ -4508,7 +4516,7 @@
       <c r="O318" s="10"/>
       <c r="P318" s="4"/>
     </row>
-    <row r="319" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="319" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D319" s="2"/>
       <c r="E319" s="10"/>
       <c r="H319" s="4"/>
@@ -4518,7 +4526,7 @@
       <c r="O319" s="10"/>
       <c r="P319" s="4"/>
     </row>
-    <row r="320" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="320" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D320" s="2"/>
       <c r="E320" s="10"/>
       <c r="H320" s="4"/>
@@ -4528,7 +4536,7 @@
       <c r="O320" s="10"/>
       <c r="P320" s="4"/>
     </row>
-    <row r="321" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="321" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D321" s="2"/>
       <c r="E321" s="10"/>
       <c r="H321" s="4"/>
@@ -4538,7 +4546,7 @@
       <c r="O321" s="10"/>
       <c r="P321" s="4"/>
     </row>
-    <row r="322" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="322" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D322" s="2"/>
       <c r="E322" s="10"/>
       <c r="H322" s="4"/>
@@ -4548,7 +4556,7 @@
       <c r="O322" s="10"/>
       <c r="P322" s="4"/>
     </row>
-    <row r="323" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="323" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D323" s="2"/>
       <c r="E323" s="10"/>
       <c r="H323" s="4"/>
@@ -4558,7 +4566,7 @@
       <c r="O323" s="10"/>
       <c r="P323" s="4"/>
     </row>
-    <row r="324" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="324" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D324" s="2"/>
       <c r="E324" s="10"/>
       <c r="H324" s="4"/>
@@ -4568,7 +4576,7 @@
       <c r="O324" s="10"/>
       <c r="P324" s="4"/>
     </row>
-    <row r="325" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="325" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D325" s="2"/>
       <c r="E325" s="10"/>
       <c r="H325" s="4"/>
@@ -4578,7 +4586,7 @@
       <c r="O325" s="10"/>
       <c r="P325" s="4"/>
     </row>
-    <row r="326" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="326" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D326" s="2"/>
       <c r="E326" s="10"/>
       <c r="H326" s="4"/>
@@ -4588,7 +4596,7 @@
       <c r="O326" s="10"/>
       <c r="P326" s="4"/>
     </row>
-    <row r="327" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="327" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D327" s="2"/>
       <c r="E327" s="10"/>
       <c r="H327" s="4"/>
@@ -4598,7 +4606,7 @@
       <c r="O327" s="10"/>
       <c r="P327" s="4"/>
     </row>
-    <row r="328" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="328" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D328" s="2"/>
       <c r="E328" s="10"/>
       <c r="H328" s="4"/>
@@ -4608,7 +4616,7 @@
       <c r="O328" s="10"/>
       <c r="P328" s="4"/>
     </row>
-    <row r="329" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="329" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D329" s="2"/>
       <c r="E329" s="10"/>
       <c r="H329" s="4"/>
@@ -4618,7 +4626,7 @@
       <c r="O329" s="10"/>
       <c r="P329" s="4"/>
     </row>
-    <row r="330" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="330" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D330" s="2"/>
       <c r="E330" s="10"/>
       <c r="H330" s="4"/>
@@ -4628,7 +4636,7 @@
       <c r="O330" s="10"/>
       <c r="P330" s="4"/>
     </row>
-    <row r="331" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="331" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D331" s="2"/>
       <c r="E331" s="10"/>
       <c r="H331" s="4"/>
@@ -4638,7 +4646,7 @@
       <c r="O331" s="10"/>
       <c r="P331" s="4"/>
     </row>
-    <row r="332" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="332" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D332" s="2"/>
       <c r="E332" s="10"/>
       <c r="H332" s="4"/>
@@ -4648,7 +4656,7 @@
       <c r="O332" s="10"/>
       <c r="P332" s="4"/>
     </row>
-    <row r="333" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="333" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D333" s="2"/>
       <c r="E333" s="10"/>
       <c r="H333" s="4"/>
@@ -4658,7 +4666,7 @@
       <c r="O333" s="10"/>
       <c r="P333" s="4"/>
     </row>
-    <row r="334" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="334" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D334" s="2"/>
       <c r="E334" s="10"/>
       <c r="H334" s="4"/>
@@ -4668,7 +4676,7 @@
       <c r="O334" s="10"/>
       <c r="P334" s="4"/>
     </row>
-    <row r="335" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="335" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D335" s="2"/>
       <c r="E335" s="10"/>
       <c r="H335" s="4"/>
@@ -4678,7 +4686,7 @@
       <c r="O335" s="10"/>
       <c r="P335" s="4"/>
     </row>
-    <row r="336" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="336" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D336" s="2"/>
       <c r="E336" s="10"/>
       <c r="H336" s="4"/>
@@ -4688,7 +4696,7 @@
       <c r="O336" s="10"/>
       <c r="P336" s="4"/>
     </row>
-    <row r="337" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="337" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D337" s="2"/>
       <c r="E337" s="10"/>
       <c r="H337" s="4"/>
@@ -4698,7 +4706,7 @@
       <c r="O337" s="10"/>
       <c r="P337" s="4"/>
     </row>
-    <row r="338" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="338" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D338" s="2"/>
       <c r="E338" s="10"/>
       <c r="H338" s="4"/>
@@ -4708,7 +4716,7 @@
       <c r="O338" s="10"/>
       <c r="P338" s="4"/>
     </row>
-    <row r="339" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="339" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D339" s="2"/>
       <c r="E339" s="10"/>
       <c r="H339" s="4"/>
@@ -4718,7 +4726,7 @@
       <c r="O339" s="10"/>
       <c r="P339" s="4"/>
     </row>
-    <row r="340" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="340" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D340" s="2"/>
       <c r="E340" s="10"/>
       <c r="H340" s="4"/>
@@ -4728,7 +4736,7 @@
       <c r="O340" s="10"/>
       <c r="P340" s="4"/>
     </row>
-    <row r="341" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="341" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D341" s="2"/>
       <c r="E341" s="10"/>
       <c r="H341" s="4"/>
@@ -4738,7 +4746,7 @@
       <c r="O341" s="10"/>
       <c r="P341" s="4"/>
     </row>
-    <row r="342" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="342" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D342" s="2"/>
       <c r="E342" s="10"/>
       <c r="H342" s="4"/>
@@ -4748,7 +4756,7 @@
       <c r="O342" s="10"/>
       <c r="P342" s="4"/>
     </row>
-    <row r="343" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="343" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D343" s="2"/>
       <c r="E343" s="10"/>
       <c r="H343" s="4"/>
@@ -4758,7 +4766,7 @@
       <c r="O343" s="10"/>
       <c r="P343" s="4"/>
     </row>
-    <row r="344" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="344" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D344" s="2"/>
       <c r="E344" s="10"/>
       <c r="H344" s="4"/>
@@ -4768,7 +4776,7 @@
       <c r="O344" s="10"/>
       <c r="P344" s="4"/>
     </row>
-    <row r="345" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="345" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D345" s="2"/>
       <c r="E345" s="10"/>
       <c r="H345" s="4"/>
@@ -4778,7 +4786,7 @@
       <c r="O345" s="10"/>
       <c r="P345" s="4"/>
     </row>
-    <row r="346" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="346" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D346" s="2"/>
       <c r="E346" s="10"/>
       <c r="H346" s="4"/>
@@ -4788,7 +4796,7 @@
       <c r="O346" s="10"/>
       <c r="P346" s="4"/>
     </row>
-    <row r="347" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="347" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D347" s="2"/>
       <c r="E347" s="10"/>
       <c r="H347" s="4"/>
@@ -4798,7 +4806,7 @@
       <c r="O347" s="10"/>
       <c r="P347" s="4"/>
     </row>
-    <row r="348" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="348" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D348" s="2"/>
       <c r="E348" s="10"/>
       <c r="H348" s="4"/>
@@ -4808,7 +4816,7 @@
       <c r="O348" s="10"/>
       <c r="P348" s="4"/>
     </row>
-    <row r="349" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="349" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D349" s="2"/>
       <c r="E349" s="10"/>
       <c r="H349" s="4"/>
@@ -4818,7 +4826,7 @@
       <c r="O349" s="10"/>
       <c r="P349" s="4"/>
     </row>
-    <row r="350" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="350" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D350" s="2"/>
       <c r="E350" s="10"/>
       <c r="H350" s="4"/>
@@ -4828,7 +4836,7 @@
       <c r="O350" s="10"/>
       <c r="P350" s="4"/>
     </row>
-    <row r="351" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="351" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D351" s="2"/>
       <c r="E351" s="10"/>
       <c r="H351" s="4"/>
@@ -4838,7 +4846,7 @@
       <c r="O351" s="10"/>
       <c r="P351" s="4"/>
     </row>
-    <row r="352" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="352" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D352" s="2"/>
       <c r="E352" s="10"/>
       <c r="H352" s="4"/>
@@ -4848,7 +4856,7 @@
       <c r="O352" s="10"/>
       <c r="P352" s="4"/>
     </row>
-    <row r="353" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="353" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D353" s="2"/>
       <c r="E353" s="10"/>
       <c r="H353" s="4"/>
@@ -4858,7 +4866,7 @@
       <c r="O353" s="10"/>
       <c r="P353" s="4"/>
     </row>
-    <row r="354" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="354" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D354" s="2"/>
       <c r="E354" s="10"/>
       <c r="H354" s="4"/>
@@ -4868,7 +4876,7 @@
       <c r="O354" s="10"/>
       <c r="P354" s="4"/>
     </row>
-    <row r="355" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="355" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D355" s="2"/>
       <c r="E355" s="10"/>
       <c r="H355" s="4"/>
@@ -4878,7 +4886,7 @@
       <c r="O355" s="10"/>
       <c r="P355" s="4"/>
     </row>
-    <row r="356" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="356" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D356" s="2"/>
       <c r="E356" s="10"/>
       <c r="H356" s="4"/>
@@ -4888,7 +4896,7 @@
       <c r="O356" s="10"/>
       <c r="P356" s="4"/>
     </row>
-    <row r="357" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="357" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D357" s="2"/>
       <c r="E357" s="10"/>
       <c r="H357" s="4"/>
@@ -4898,7 +4906,7 @@
       <c r="O357" s="10"/>
       <c r="P357" s="4"/>
     </row>
-    <row r="358" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="358" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D358" s="2"/>
       <c r="E358" s="10"/>
       <c r="H358" s="4"/>
@@ -4908,7 +4916,7 @@
       <c r="O358" s="10"/>
       <c r="P358" s="4"/>
     </row>
-    <row r="359" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="359" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D359" s="2"/>
       <c r="E359" s="10"/>
       <c r="H359" s="4"/>
@@ -4918,7 +4926,7 @@
       <c r="O359" s="10"/>
       <c r="P359" s="4"/>
     </row>
-    <row r="360" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="360" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D360" s="2"/>
       <c r="E360" s="10"/>
       <c r="H360" s="4"/>
@@ -4928,7 +4936,7 @@
       <c r="O360" s="10"/>
       <c r="P360" s="4"/>
     </row>
-    <row r="361" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="361" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D361" s="2"/>
       <c r="E361" s="10"/>
       <c r="H361" s="4"/>
@@ -4938,7 +4946,7 @@
       <c r="O361" s="10"/>
       <c r="P361" s="4"/>
     </row>
-    <row r="362" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="362" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D362" s="2"/>
       <c r="E362" s="10"/>
       <c r="H362" s="4"/>
@@ -4948,7 +4956,7 @@
       <c r="O362" s="10"/>
       <c r="P362" s="4"/>
     </row>
-    <row r="363" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="363" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D363" s="2"/>
       <c r="E363" s="10"/>
       <c r="H363" s="4"/>
@@ -4958,7 +4966,7 @@
       <c r="O363" s="10"/>
       <c r="P363" s="4"/>
     </row>
-    <row r="364" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="364" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D364" s="2"/>
       <c r="E364" s="10"/>
       <c r="H364" s="4"/>
@@ -4968,7 +4976,7 @@
       <c r="O364" s="10"/>
       <c r="P364" s="4"/>
     </row>
-    <row r="365" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="365" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D365" s="2"/>
       <c r="E365" s="10"/>
       <c r="H365" s="4"/>
@@ -4978,7 +4986,7 @@
       <c r="O365" s="10"/>
       <c r="P365" s="4"/>
     </row>
-    <row r="366" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="366" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D366" s="2"/>
       <c r="E366" s="10"/>
       <c r="H366" s="4"/>
@@ -4988,7 +4996,7 @@
       <c r="O366" s="10"/>
       <c r="P366" s="4"/>
     </row>
-    <row r="367" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="367" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D367" s="2"/>
       <c r="E367" s="10"/>
       <c r="H367" s="4"/>
@@ -4998,7 +5006,7 @@
       <c r="O367" s="10"/>
       <c r="P367" s="4"/>
     </row>
-    <row r="368" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="368" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D368" s="2"/>
       <c r="E368" s="10"/>
       <c r="H368" s="4"/>
@@ -5008,7 +5016,7 @@
       <c r="O368" s="10"/>
       <c r="P368" s="4"/>
     </row>
-    <row r="369" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="369" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D369" s="2"/>
       <c r="E369" s="10"/>
       <c r="H369" s="4"/>
@@ -5018,7 +5026,7 @@
       <c r="O369" s="10"/>
       <c r="P369" s="4"/>
     </row>
-    <row r="370" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="370" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D370" s="2"/>
       <c r="E370" s="10"/>
       <c r="H370" s="4"/>
@@ -5028,7 +5036,7 @@
       <c r="O370" s="10"/>
       <c r="P370" s="4"/>
     </row>
-    <row r="371" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="371" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D371" s="2"/>
       <c r="E371" s="10"/>
       <c r="H371" s="4"/>
@@ -5038,7 +5046,7 @@
       <c r="O371" s="10"/>
       <c r="P371" s="4"/>
     </row>
-    <row r="372" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="372" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D372" s="2"/>
       <c r="E372" s="10"/>
       <c r="H372" s="4"/>
@@ -5048,7 +5056,7 @@
       <c r="O372" s="10"/>
       <c r="P372" s="4"/>
     </row>
-    <row r="373" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="373" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D373" s="2"/>
       <c r="E373" s="10"/>
       <c r="H373" s="4"/>
@@ -5058,7 +5066,7 @@
       <c r="O373" s="10"/>
       <c r="P373" s="4"/>
     </row>
-    <row r="374" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="374" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D374" s="2"/>
       <c r="E374" s="10"/>
       <c r="H374" s="4"/>
@@ -5068,7 +5076,7 @@
       <c r="O374" s="10"/>
       <c r="P374" s="4"/>
     </row>
-    <row r="375" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="375" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D375" s="2"/>
       <c r="E375" s="10"/>
       <c r="H375" s="4"/>
@@ -5078,7 +5086,7 @@
       <c r="O375" s="10"/>
       <c r="P375" s="4"/>
     </row>
-    <row r="376" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="376" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D376" s="2"/>
       <c r="E376" s="10"/>
       <c r="H376" s="4"/>
@@ -5088,7 +5096,7 @@
       <c r="O376" s="10"/>
       <c r="P376" s="4"/>
     </row>
-    <row r="377" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="377" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D377" s="2"/>
       <c r="E377" s="10"/>
       <c r="H377" s="4"/>
@@ -5098,7 +5106,7 @@
       <c r="O377" s="10"/>
       <c r="P377" s="4"/>
     </row>
-    <row r="378" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="378" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D378" s="2"/>
       <c r="E378" s="10"/>
       <c r="H378" s="4"/>
@@ -5108,7 +5116,7 @@
       <c r="O378" s="10"/>
       <c r="P378" s="4"/>
     </row>
-    <row r="379" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="379" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D379" s="2"/>
       <c r="E379" s="10"/>
       <c r="H379" s="4"/>
@@ -5118,7 +5126,7 @@
       <c r="O379" s="10"/>
       <c r="P379" s="4"/>
     </row>
-    <row r="380" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="380" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D380" s="2"/>
       <c r="E380" s="10"/>
       <c r="H380" s="4"/>
@@ -5128,7 +5136,7 @@
       <c r="O380" s="10"/>
       <c r="P380" s="4"/>
     </row>
-    <row r="381" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="381" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D381" s="2"/>
       <c r="E381" s="10"/>
       <c r="H381" s="4"/>
@@ -5138,7 +5146,7 @@
       <c r="O381" s="10"/>
       <c r="P381" s="4"/>
     </row>
-    <row r="382" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="382" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D382" s="2"/>
       <c r="E382" s="10"/>
       <c r="H382" s="4"/>
@@ -5148,7 +5156,7 @@
       <c r="O382" s="10"/>
       <c r="P382" s="4"/>
     </row>
-    <row r="383" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="383" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D383" s="2"/>
       <c r="E383" s="10"/>
       <c r="H383" s="4"/>
@@ -5158,7 +5166,7 @@
       <c r="O383" s="10"/>
       <c r="P383" s="4"/>
     </row>
-    <row r="384" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="384" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D384" s="2"/>
       <c r="E384" s="10"/>
       <c r="H384" s="4"/>
@@ -5168,7 +5176,7 @@
       <c r="O384" s="10"/>
       <c r="P384" s="4"/>
     </row>
-    <row r="385" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="385" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D385" s="2"/>
       <c r="E385" s="10"/>
       <c r="H385" s="4"/>
@@ -5178,7 +5186,7 @@
       <c r="O385" s="10"/>
       <c r="P385" s="4"/>
     </row>
-    <row r="386" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="386" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D386" s="2"/>
       <c r="E386" s="10"/>
       <c r="H386" s="4"/>
@@ -5188,7 +5196,7 @@
       <c r="O386" s="10"/>
       <c r="P386" s="4"/>
     </row>
-    <row r="387" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="387" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D387" s="2"/>
       <c r="E387" s="10"/>
       <c r="H387" s="4"/>
@@ -5198,7 +5206,7 @@
       <c r="O387" s="10"/>
       <c r="P387" s="4"/>
     </row>
-    <row r="388" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="388" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D388" s="2"/>
       <c r="E388" s="10"/>
       <c r="H388" s="4"/>
@@ -5208,7 +5216,7 @@
       <c r="O388" s="10"/>
       <c r="P388" s="4"/>
     </row>
-    <row r="389" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="389" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D389" s="2"/>
       <c r="E389" s="10"/>
       <c r="H389" s="4"/>
@@ -5218,7 +5226,7 @@
       <c r="O389" s="10"/>
       <c r="P389" s="4"/>
     </row>
-    <row r="390" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="390" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D390" s="2"/>
       <c r="E390" s="10"/>
       <c r="H390" s="4"/>
@@ -5228,7 +5236,7 @@
       <c r="O390" s="10"/>
       <c r="P390" s="4"/>
     </row>
-    <row r="391" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="391" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D391" s="2"/>
       <c r="E391" s="10"/>
       <c r="H391" s="4"/>
@@ -5238,7 +5246,7 @@
       <c r="O391" s="10"/>
       <c r="P391" s="4"/>
     </row>
-    <row r="392" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="392" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D392" s="2"/>
       <c r="E392" s="10"/>
       <c r="H392" s="4"/>
@@ -5248,7 +5256,7 @@
       <c r="O392" s="10"/>
       <c r="P392" s="4"/>
     </row>
-    <row r="393" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="393" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D393" s="2"/>
       <c r="E393" s="10"/>
       <c r="H393" s="4"/>
@@ -5258,7 +5266,7 @@
       <c r="O393" s="10"/>
       <c r="P393" s="4"/>
     </row>
-    <row r="394" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="394" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D394" s="2"/>
       <c r="E394" s="10"/>
       <c r="H394" s="4"/>
@@ -5268,7 +5276,7 @@
       <c r="O394" s="10"/>
       <c r="P394" s="4"/>
     </row>
-    <row r="395" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="395" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D395" s="2"/>
       <c r="E395" s="10"/>
       <c r="H395" s="4"/>
@@ -5278,7 +5286,7 @@
       <c r="O395" s="10"/>
       <c r="P395" s="4"/>
     </row>
-    <row r="396" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="396" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D396" s="2"/>
       <c r="E396" s="10"/>
       <c r="H396" s="4"/>
@@ -5288,7 +5296,7 @@
       <c r="O396" s="10"/>
       <c r="P396" s="4"/>
     </row>
-    <row r="397" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="397" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D397" s="2"/>
       <c r="E397" s="10"/>
       <c r="H397" s="4"/>
@@ -5298,7 +5306,7 @@
       <c r="O397" s="10"/>
       <c r="P397" s="4"/>
     </row>
-    <row r="398" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="398" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D398" s="2"/>
       <c r="E398" s="10"/>
       <c r="H398" s="4"/>
@@ -5308,7 +5316,7 @@
       <c r="O398" s="10"/>
       <c r="P398" s="4"/>
     </row>
-    <row r="399" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="399" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D399" s="2"/>
       <c r="E399" s="10"/>
       <c r="H399" s="4"/>
@@ -5318,7 +5326,7 @@
       <c r="O399" s="10"/>
       <c r="P399" s="4"/>
     </row>
-    <row r="400" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="400" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D400" s="2"/>
       <c r="E400" s="10"/>
       <c r="H400" s="4"/>
@@ -5328,7 +5336,7 @@
       <c r="O400" s="10"/>
       <c r="P400" s="4"/>
     </row>
-    <row r="401" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="401" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D401" s="2"/>
       <c r="E401" s="10"/>
       <c r="H401" s="4"/>
@@ -5338,7 +5346,7 @@
       <c r="O401" s="10"/>
       <c r="P401" s="4"/>
     </row>
-    <row r="402" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="402" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D402" s="2"/>
       <c r="E402" s="10"/>
       <c r="H402" s="4"/>
@@ -5348,7 +5356,7 @@
       <c r="O402" s="10"/>
       <c r="P402" s="4"/>
     </row>
-    <row r="403" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="403" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D403" s="2"/>
       <c r="E403" s="10"/>
       <c r="H403" s="4"/>
@@ -5358,7 +5366,7 @@
       <c r="O403" s="10"/>
       <c r="P403" s="4"/>
     </row>
-    <row r="404" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="404" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D404" s="2"/>
       <c r="E404" s="10"/>
       <c r="H404" s="4"/>
@@ -5368,7 +5376,7 @@
       <c r="O404" s="10"/>
       <c r="P404" s="4"/>
     </row>
-    <row r="405" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="405" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D405" s="2"/>
       <c r="E405" s="10"/>
       <c r="H405" s="4"/>
@@ -5378,7 +5386,7 @@
       <c r="O405" s="10"/>
       <c r="P405" s="4"/>
     </row>
-    <row r="406" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="406" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D406" s="2"/>
       <c r="E406" s="10"/>
       <c r="H406" s="4"/>
@@ -5388,7 +5396,7 @@
       <c r="O406" s="10"/>
       <c r="P406" s="4"/>
     </row>
-    <row r="407" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="407" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D407" s="2"/>
       <c r="E407" s="10"/>
       <c r="H407" s="4"/>
@@ -5398,7 +5406,7 @@
       <c r="O407" s="10"/>
       <c r="P407" s="4"/>
     </row>
-    <row r="408" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="408" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D408" s="2"/>
       <c r="E408" s="10"/>
       <c r="H408" s="4"/>
@@ -5408,7 +5416,7 @@
       <c r="O408" s="10"/>
       <c r="P408" s="4"/>
     </row>
-    <row r="409" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="409" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D409" s="2"/>
       <c r="E409" s="10"/>
       <c r="H409" s="4"/>
@@ -5418,7 +5426,7 @@
       <c r="O409" s="10"/>
       <c r="P409" s="4"/>
     </row>
-    <row r="410" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="410" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D410" s="2"/>
       <c r="E410" s="10"/>
       <c r="H410" s="4"/>
@@ -5428,7 +5436,7 @@
       <c r="O410" s="10"/>
       <c r="P410" s="4"/>
     </row>
-    <row r="411" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="411" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D411" s="2"/>
       <c r="E411" s="10"/>
       <c r="H411" s="4"/>
@@ -5438,7 +5446,7 @@
       <c r="O411" s="10"/>
       <c r="P411" s="4"/>
     </row>
-    <row r="412" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="412" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D412" s="2"/>
       <c r="E412" s="10"/>
       <c r="H412" s="4"/>
@@ -5448,7 +5456,7 @@
       <c r="O412" s="10"/>
       <c r="P412" s="4"/>
     </row>
-    <row r="413" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="413" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D413" s="2"/>
       <c r="E413" s="10"/>
       <c r="H413" s="4"/>
@@ -5458,7 +5466,7 @@
       <c r="O413" s="10"/>
       <c r="P413" s="4"/>
     </row>
-    <row r="414" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="414" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D414" s="2"/>
       <c r="E414" s="10"/>
       <c r="H414" s="4"/>
@@ -5468,7 +5476,7 @@
       <c r="O414" s="10"/>
       <c r="P414" s="4"/>
     </row>
-    <row r="415" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="415" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D415" s="2"/>
       <c r="E415" s="10"/>
       <c r="H415" s="4"/>
@@ -5478,7 +5486,7 @@
       <c r="O415" s="10"/>
       <c r="P415" s="4"/>
     </row>
-    <row r="416" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="416" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D416" s="2"/>
       <c r="E416" s="10"/>
       <c r="H416" s="4"/>
@@ -5488,7 +5496,7 @@
       <c r="O416" s="10"/>
       <c r="P416" s="4"/>
     </row>
-    <row r="417" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="417" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D417" s="2"/>
       <c r="E417" s="10"/>
       <c r="H417" s="4"/>
@@ -5498,7 +5506,7 @@
       <c r="O417" s="10"/>
       <c r="P417" s="4"/>
     </row>
-    <row r="418" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="418" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D418" s="2"/>
       <c r="E418" s="10"/>
       <c r="H418" s="4"/>
@@ -5508,7 +5516,7 @@
       <c r="O418" s="10"/>
       <c r="P418" s="4"/>
     </row>
-    <row r="419" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="419" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D419" s="2"/>
       <c r="E419" s="10"/>
       <c r="H419" s="4"/>
@@ -5518,7 +5526,7 @@
       <c r="O419" s="10"/>
       <c r="P419" s="4"/>
     </row>
-    <row r="420" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="420" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D420" s="2"/>
       <c r="E420" s="10"/>
       <c r="H420" s="4"/>
@@ -5528,7 +5536,7 @@
       <c r="O420" s="10"/>
       <c r="P420" s="4"/>
     </row>
-    <row r="421" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="421" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D421" s="2"/>
       <c r="E421" s="10"/>
       <c r="H421" s="4"/>
@@ -5538,7 +5546,7 @@
       <c r="O421" s="10"/>
       <c r="P421" s="4"/>
     </row>
-    <row r="422" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="422" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D422" s="2"/>
       <c r="E422" s="10"/>
       <c r="H422" s="4"/>
@@ -5548,7 +5556,7 @@
       <c r="O422" s="10"/>
       <c r="P422" s="4"/>
     </row>
-    <row r="423" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="423" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D423" s="2"/>
       <c r="E423" s="10"/>
       <c r="H423" s="4"/>
@@ -5558,7 +5566,7 @@
       <c r="O423" s="10"/>
       <c r="P423" s="4"/>
     </row>
-    <row r="424" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="424" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D424" s="2"/>
       <c r="E424" s="10"/>
       <c r="H424" s="4"/>
@@ -5568,7 +5576,7 @@
       <c r="O424" s="10"/>
       <c r="P424" s="4"/>
     </row>
-    <row r="425" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="425" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D425" s="2"/>
       <c r="E425" s="10"/>
       <c r="H425" s="4"/>
@@ -5578,7 +5586,7 @@
       <c r="O425" s="10"/>
       <c r="P425" s="4"/>
     </row>
-    <row r="426" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="426" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D426" s="2"/>
       <c r="E426" s="10"/>
       <c r="H426" s="4"/>
@@ -5588,7 +5596,7 @@
       <c r="O426" s="10"/>
       <c r="P426" s="4"/>
     </row>
-    <row r="427" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="427" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D427" s="2"/>
       <c r="E427" s="10"/>
       <c r="H427" s="4"/>
@@ -5598,7 +5606,7 @@
       <c r="O427" s="10"/>
       <c r="P427" s="4"/>
     </row>
-    <row r="428" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="428" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D428" s="2"/>
       <c r="E428" s="10"/>
       <c r="H428" s="4"/>
@@ -5608,7 +5616,7 @@
       <c r="O428" s="10"/>
       <c r="P428" s="4"/>
     </row>
-    <row r="429" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="429" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D429" s="2"/>
       <c r="E429" s="10"/>
       <c r="H429" s="4"/>
@@ -5618,7 +5626,7 @@
       <c r="O429" s="10"/>
       <c r="P429" s="4"/>
     </row>
-    <row r="430" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="430" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D430" s="2"/>
       <c r="E430" s="10"/>
       <c r="H430" s="4"/>
@@ -5628,7 +5636,7 @@
       <c r="O430" s="10"/>
       <c r="P430" s="4"/>
     </row>
-    <row r="431" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="431" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D431" s="2"/>
       <c r="E431" s="10"/>
       <c r="H431" s="4"/>
@@ -5638,7 +5646,7 @@
       <c r="O431" s="10"/>
       <c r="P431" s="4"/>
     </row>
-    <row r="432" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="432" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D432" s="2"/>
       <c r="E432" s="10"/>
       <c r="H432" s="4"/>
@@ -5648,7 +5656,7 @@
       <c r="O432" s="10"/>
       <c r="P432" s="4"/>
     </row>
-    <row r="433" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="433" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D433" s="2"/>
       <c r="E433" s="10"/>
       <c r="H433" s="4"/>
@@ -5658,7 +5666,7 @@
       <c r="O433" s="10"/>
       <c r="P433" s="4"/>
     </row>
-    <row r="434" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="434" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D434" s="2"/>
       <c r="E434" s="10"/>
       <c r="H434" s="4"/>
@@ -5668,7 +5676,7 @@
       <c r="O434" s="10"/>
       <c r="P434" s="4"/>
     </row>
-    <row r="435" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="435" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D435" s="2"/>
       <c r="E435" s="10"/>
       <c r="H435" s="4"/>
@@ -5678,7 +5686,7 @@
       <c r="O435" s="10"/>
       <c r="P435" s="4"/>
     </row>
-    <row r="436" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="436" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D436" s="2"/>
       <c r="E436" s="10"/>
       <c r="H436" s="4"/>
@@ -5688,7 +5696,7 @@
       <c r="O436" s="10"/>
       <c r="P436" s="4"/>
     </row>
-    <row r="437" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="437" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D437" s="2"/>
       <c r="E437" s="10"/>
       <c r="H437" s="4"/>
@@ -5698,7 +5706,7 @@
       <c r="O437" s="10"/>
       <c r="P437" s="4"/>
     </row>
-    <row r="438" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="438" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D438" s="2"/>
       <c r="E438" s="10"/>
       <c r="H438" s="4"/>
@@ -5708,7 +5716,7 @@
       <c r="O438" s="10"/>
       <c r="P438" s="4"/>
     </row>
-    <row r="439" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="439" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D439" s="2"/>
       <c r="E439" s="10"/>
       <c r="H439" s="4"/>
@@ -5718,7 +5726,7 @@
       <c r="O439" s="10"/>
       <c r="P439" s="4"/>
     </row>
-    <row r="440" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="440" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D440" s="2"/>
       <c r="E440" s="10"/>
       <c r="H440" s="4"/>
@@ -5728,7 +5736,7 @@
       <c r="O440" s="10"/>
       <c r="P440" s="4"/>
     </row>
-    <row r="441" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="441" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D441" s="2"/>
       <c r="E441" s="10"/>
       <c r="H441" s="4"/>
@@ -5738,7 +5746,7 @@
       <c r="O441" s="10"/>
       <c r="P441" s="4"/>
     </row>
-    <row r="442" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="442" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D442" s="2"/>
       <c r="E442" s="10"/>
       <c r="H442" s="4"/>
@@ -5748,7 +5756,7 @@
       <c r="O442" s="10"/>
       <c r="P442" s="4"/>
     </row>
-    <row r="443" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="443" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D443" s="2"/>
       <c r="E443" s="10"/>
       <c r="H443" s="4"/>
@@ -5758,7 +5766,7 @@
       <c r="O443" s="10"/>
       <c r="P443" s="4"/>
     </row>
-    <row r="444" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="444" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D444" s="2"/>
       <c r="E444" s="10"/>
       <c r="H444" s="4"/>
@@ -5766,7 +5774,7 @@
       <c r="M444" s="4"/>
       <c r="O444" s="10"/>
     </row>
-    <row r="445" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="445" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D445" s="2"/>
       <c r="E445" s="10"/>
       <c r="H445" s="4"/>
@@ -5774,7 +5782,7 @@
       <c r="M445" s="4"/>
       <c r="O445" s="10"/>
     </row>
-    <row r="446" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="446" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D446" s="2"/>
       <c r="E446" s="10"/>
       <c r="H446" s="4"/>
@@ -5782,7 +5790,7 @@
       <c r="M446" s="4"/>
       <c r="O446" s="10"/>
     </row>
-    <row r="447" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="447" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D447" s="2"/>
       <c r="E447" s="10"/>
       <c r="H447" s="4"/>
@@ -5790,7 +5798,7 @@
       <c r="M447" s="4"/>
       <c r="O447" s="10"/>
     </row>
-    <row r="448" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="448" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D448" s="2"/>
       <c r="E448" s="10"/>
       <c r="H448" s="4"/>
@@ -5798,7 +5806,7 @@
       <c r="M448" s="4"/>
       <c r="O448" s="10"/>
     </row>
-    <row r="449" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="449" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D449" s="2"/>
       <c r="E449" s="10"/>
       <c r="H449" s="4"/>
@@ -5806,7 +5814,7 @@
       <c r="M449" s="4"/>
       <c r="O449" s="10"/>
     </row>
-    <row r="450" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="450" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D450" s="2"/>
       <c r="E450" s="10"/>
       <c r="H450" s="6"/>
@@ -5814,7 +5822,7 @@
       <c r="M450" s="4"/>
       <c r="O450" s="10"/>
     </row>
-    <row r="451" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="451" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D451" s="2"/>
       <c r="E451" s="10"/>
       <c r="H451" s="4"/>
@@ -5822,7 +5830,7 @@
       <c r="M451" s="4"/>
       <c r="O451" s="10"/>
     </row>
-    <row r="452" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="452" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D452" s="2"/>
       <c r="E452" s="10"/>
       <c r="H452" s="6"/>
@@ -5830,7 +5838,7 @@
       <c r="M452" s="4"/>
       <c r="O452" s="10"/>
     </row>
-    <row r="453" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="453" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D453" s="2"/>
       <c r="E453" s="10"/>
       <c r="H453" s="4"/>
@@ -5838,7 +5846,7 @@
       <c r="M453" s="4"/>
       <c r="O453" s="10"/>
     </row>
-    <row r="454" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="454" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D454" s="2"/>
       <c r="E454" s="10"/>
       <c r="H454" s="4"/>
@@ -5846,7 +5854,7 @@
       <c r="M454" s="4"/>
       <c r="O454" s="10"/>
     </row>
-    <row r="455" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="455" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D455" s="2"/>
       <c r="E455" s="10"/>
       <c r="H455" s="4"/>
@@ -5854,7 +5862,7 @@
       <c r="M455" s="4"/>
       <c r="O455" s="10"/>
     </row>
-    <row r="456" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="456" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D456" s="2"/>
       <c r="E456" s="10"/>
       <c r="H456" s="4"/>
@@ -5862,7 +5870,7 @@
       <c r="M456" s="4"/>
       <c r="O456" s="10"/>
     </row>
-    <row r="457" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="457" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D457" s="2"/>
       <c r="E457" s="10"/>
       <c r="H457" s="4"/>
@@ -5870,7 +5878,7 @@
       <c r="M457" s="4"/>
       <c r="O457" s="10"/>
     </row>
-    <row r="458" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="458" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D458" s="2"/>
       <c r="E458" s="10"/>
       <c r="H458" s="4"/>
@@ -5878,7 +5886,7 @@
       <c r="M458" s="4"/>
       <c r="O458" s="10"/>
     </row>
-    <row r="459" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="459" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D459" s="2"/>
       <c r="E459" s="10"/>
       <c r="H459" s="4"/>
@@ -5886,7 +5894,7 @@
       <c r="M459" s="4"/>
       <c r="O459" s="10"/>
     </row>
-    <row r="460" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="460" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D460" s="2"/>
       <c r="E460" s="10"/>
       <c r="H460" s="4"/>
@@ -5894,7 +5902,7 @@
       <c r="M460" s="4"/>
       <c r="O460" s="10"/>
     </row>
-    <row r="461" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="461" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D461" s="2"/>
       <c r="E461" s="10"/>
       <c r="H461" s="4"/>
@@ -5902,7 +5910,7 @@
       <c r="M461" s="4"/>
       <c r="O461" s="10"/>
     </row>
-    <row r="462" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="462" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D462" s="2"/>
       <c r="E462" s="10"/>
       <c r="H462" s="4"/>
@@ -5910,7 +5918,7 @@
       <c r="M462" s="4"/>
       <c r="O462" s="10"/>
     </row>
-    <row r="463" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="463" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D463" s="2"/>
       <c r="E463" s="10"/>
       <c r="H463" s="4"/>
@@ -5918,7 +5926,7 @@
       <c r="M463" s="4"/>
       <c r="O463" s="10"/>
     </row>
-    <row r="464" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="464" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D464" s="2"/>
       <c r="E464" s="10"/>
       <c r="H464" s="6"/>
@@ -5926,7 +5934,7 @@
       <c r="M464" s="4"/>
       <c r="O464" s="10"/>
     </row>
-    <row r="465" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="465" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D465" s="2"/>
       <c r="E465" s="10"/>
       <c r="H465" s="4"/>
@@ -5934,7 +5942,7 @@
       <c r="M465" s="4"/>
       <c r="O465" s="10"/>
     </row>
-    <row r="466" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="466" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D466" s="2"/>
       <c r="E466" s="10"/>
       <c r="H466" s="6"/>
@@ -5942,7 +5950,7 @@
       <c r="M466" s="4"/>
       <c r="O466" s="10"/>
     </row>
-    <row r="467" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="467" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D467" s="2"/>
       <c r="E467" s="10"/>
       <c r="H467" s="4"/>
@@ -5950,7 +5958,7 @@
       <c r="M467" s="4"/>
       <c r="O467" s="10"/>
     </row>
-    <row r="468" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="468" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D468" s="2"/>
       <c r="E468" s="10"/>
       <c r="H468" s="4"/>
@@ -5958,7 +5966,7 @@
       <c r="M468" s="4"/>
       <c r="O468" s="10"/>
     </row>
-    <row r="469" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="469" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D469" s="2"/>
       <c r="E469" s="10"/>
       <c r="H469" s="4"/>
@@ -5966,7 +5974,7 @@
       <c r="M469" s="4"/>
       <c r="O469" s="10"/>
     </row>
-    <row r="470" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="470" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D470" s="2"/>
       <c r="E470" s="10"/>
       <c r="H470" s="4"/>
@@ -5974,14 +5982,14 @@
       <c r="M470" s="4"/>
       <c r="O470" s="10"/>
     </row>
-    <row r="471" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="471" spans="4:15" x14ac:dyDescent="0.25">
       <c r="E471" s="10"/>
       <c r="H471" s="4"/>
       <c r="J471" s="5"/>
       <c r="M471" s="4"/>
       <c r="O471" s="10"/>
     </row>
-    <row r="472" spans="4:15" x14ac:dyDescent="0.3">
+    <row r="472" spans="4:15" x14ac:dyDescent="0.25">
       <c r="E472" s="10"/>
       <c r="H472" s="4"/>
       <c r="J472" s="5"/>
@@ -6000,13 +6008,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC130FB4-2F37-4474-8AA2-B01341A5EC99}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.88671875" customWidth="1"/>
-    <col min="2" max="2" width="52.6640625" customWidth="1"/>
+    <col min="1" max="1" width="57.85546875" customWidth="1"/>
+    <col min="2" max="2" width="52.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>17</v>
       </c>
@@ -6014,7 +6022,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>19</v>
       </c>
@@ -6022,7 +6030,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>20</v>
       </c>
@@ -6030,7 +6038,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>21</v>
       </c>
@@ -6038,7 +6046,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>22</v>
       </c>
@@ -6054,13 +6062,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DB5104C-39AB-4F23-89F3-98B2DF5E239C}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.6640625" customWidth="1"/>
-    <col min="2" max="2" width="66.88671875" customWidth="1"/>
+    <col min="1" max="1" width="48.7109375" customWidth="1"/>
+    <col min="2" max="2" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>17</v>
       </c>
@@ -6068,7 +6076,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>19</v>
       </c>
@@ -6076,7 +6084,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>21</v>
       </c>
@@ -6084,7 +6092,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>22</v>
       </c>
